--- a/AAII_Financials/Quarterly/CBOE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBOE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>CBOE</t>
   </si>
@@ -672,477 +672,490 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="18.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="18.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18" style="4" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="18.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18" style="4" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="18.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="18.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="18.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18" style="4" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="18.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18" style="4" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="18.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="5">
+      <c r="O7" s="5">
         <v>45199</v>
       </c>
-      <c r="O7" s="5">
+      <c r="P7" s="5">
         <v>45107</v>
       </c>
-      <c r="P7" s="5">
+      <c r="Q7" s="5">
         <v>45016</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="R7" s="5">
         <v>44926</v>
       </c>
-      <c r="R7" s="5">
+      <c r="S7" s="5">
         <v>44834</v>
       </c>
-      <c r="S7" s="5">
+      <c r="T7" s="5">
         <v>44742</v>
       </c>
-      <c r="T7" s="5">
+      <c r="U7" s="5">
         <v>44651</v>
       </c>
-      <c r="U7" s="5">
+      <c r="V7" s="5">
         <v>44561</v>
       </c>
-      <c r="V7" s="5">
+      <c r="W7" s="5">
         <v>44469</v>
       </c>
-      <c r="W7" s="5">
+      <c r="X7" s="5">
         <v>44377</v>
       </c>
-      <c r="X7" s="5">
+      <c r="Y7" s="5">
         <v>44286</v>
       </c>
-      <c r="Y7" s="5">
+      <c r="Z7" s="5">
         <v>44196</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="AA7" s="5">
         <v>44104</v>
       </c>
-      <c r="AA7" s="5">
+      <c r="AB7" s="5">
         <v>44012</v>
       </c>
-      <c r="AB7" s="5">
+      <c r="AC7" s="5">
         <v>43921</v>
       </c>
-      <c r="AC7" s="5">
+      <c r="AD7" s="5">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1442800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1272800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1204000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1141700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1173500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1195000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1107600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1055700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>974000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>957200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>968700</v>
       </c>
-      <c r="N8" s="6">
+      <c r="O8" s="6">
         <v>908800</v>
       </c>
-      <c r="O8" s="6">
+      <c r="P8" s="6">
         <v>907800</v>
       </c>
-      <c r="P8" s="6">
+      <c r="Q8" s="6">
         <v>988200</v>
       </c>
-      <c r="Q8" s="6">
+      <c r="R8" s="6">
         <v>1004700</v>
       </c>
-      <c r="R8" s="6">
+      <c r="S8" s="6">
         <v>993500</v>
       </c>
-      <c r="S8" s="6">
+      <c r="T8" s="6">
         <v>985800</v>
       </c>
-      <c r="T8" s="6">
+      <c r="U8" s="6">
         <v>974500</v>
       </c>
-      <c r="U8" s="6">
+      <c r="V8" s="6">
         <v>866400</v>
       </c>
-      <c r="V8" s="6">
+      <c r="W8" s="6">
         <v>816800</v>
       </c>
-      <c r="W8" s="6">
+      <c r="X8" s="6">
         <v>800800</v>
       </c>
-      <c r="X8" s="6">
+      <c r="Y8" s="6">
         <v>1010800</v>
       </c>
-      <c r="Y8" s="6">
+      <c r="Z8" s="6">
         <v>844200</v>
       </c>
-      <c r="Z8" s="6">
+      <c r="AA8" s="6">
         <v>792700</v>
       </c>
-      <c r="AA8" s="6">
+      <c r="AB8" s="6">
         <v>868700</v>
       </c>
-      <c r="AB8" s="6">
+      <c r="AC8" s="6">
         <v>921500</v>
       </c>
-      <c r="AC8" s="6">
+      <c r="AD8" s="6">
         <v>598600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>667500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>777700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>620700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>611400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>640800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>356200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>175100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>156200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>711200</v>
+      </c>
+      <c r="E9" s="3">
         <v>543900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>532900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>536200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>586200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>629800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>583100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>523700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>460200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>455100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>469700</v>
       </c>
-      <c r="N9" s="6">
+      <c r="O9" s="6">
         <v>428300</v>
       </c>
-      <c r="O9" s="6">
+      <c r="P9" s="6">
         <v>440700</v>
       </c>
-      <c r="P9" s="6">
+      <c r="Q9" s="6">
         <v>516800</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="R9" s="6">
         <v>547600</v>
       </c>
-      <c r="R9" s="6">
+      <c r="S9" s="6">
         <v>551100</v>
       </c>
-      <c r="S9" s="6">
+      <c r="T9" s="6">
         <v>561700</v>
       </c>
-      <c r="T9" s="6">
+      <c r="U9" s="6">
         <v>556400</v>
       </c>
-      <c r="U9" s="6">
+      <c r="V9" s="6">
         <v>475900</v>
       </c>
-      <c r="V9" s="6">
+      <c r="W9" s="6">
         <v>447300</v>
       </c>
-      <c r="W9" s="6">
+      <c r="X9" s="6">
         <v>450200</v>
       </c>
-      <c r="X9" s="6">
+      <c r="Y9" s="6">
         <v>645300</v>
       </c>
-      <c r="Y9" s="6">
+      <c r="Z9" s="6">
         <v>537100</v>
       </c>
-      <c r="Z9" s="6">
+      <c r="AA9" s="6">
         <v>500700</v>
       </c>
-      <c r="AA9" s="6">
+      <c r="AB9" s="6">
         <v>571800</v>
       </c>
-      <c r="AB9" s="6">
+      <c r="AC9" s="6">
         <v>563200</v>
       </c>
-      <c r="AC9" s="6">
+      <c r="AD9" s="6">
         <v>318300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>384000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>449200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>355100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>341700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>373900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>162800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>20100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>731600</v>
+      </c>
+      <c r="E10" s="3">
         <v>728900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>671100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>605500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>587300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>565200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>524500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>532000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>513800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>502100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>499000</v>
       </c>
-      <c r="N10" s="6">
+      <c r="O10" s="6">
         <v>480500</v>
       </c>
-      <c r="O10" s="6">
+      <c r="P10" s="6">
         <v>467100</v>
       </c>
-      <c r="P10" s="6">
+      <c r="Q10" s="6">
         <v>471400</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="R10" s="6">
         <v>457100</v>
       </c>
-      <c r="R10" s="6">
+      <c r="S10" s="6">
         <v>442400</v>
       </c>
-      <c r="S10" s="6">
+      <c r="T10" s="6">
         <v>424100</v>
       </c>
-      <c r="T10" s="6">
+      <c r="U10" s="6">
         <v>418100</v>
       </c>
-      <c r="U10" s="6">
+      <c r="V10" s="6">
         <v>390500</v>
       </c>
-      <c r="V10" s="6">
+      <c r="W10" s="6">
         <v>369500</v>
       </c>
-      <c r="W10" s="6">
+      <c r="X10" s="6">
         <v>350600</v>
       </c>
-      <c r="X10" s="6">
+      <c r="Y10" s="6">
         <v>365500</v>
       </c>
-      <c r="Y10" s="6">
+      <c r="Z10" s="6">
         <v>307100</v>
       </c>
-      <c r="Z10" s="6">
+      <c r="AA10" s="6">
         <v>292000</v>
       </c>
-      <c r="AA10" s="6">
+      <c r="AB10" s="6">
         <v>296900</v>
       </c>
-      <c r="AB10" s="6">
+      <c r="AC10" s="6">
         <v>358300</v>
       </c>
-      <c r="AC10" s="6">
+      <c r="AD10" s="6">
         <v>280300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>283500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>328500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>265600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>269700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>266900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>193400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>155000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>136800</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1156,7 +1169,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="6"/>
+      <c r="N11" s="3"/>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
@@ -1172,7 +1185,7 @@
       <c r="AA11" s="6"/>
       <c r="AB11" s="6"/>
       <c r="AC11" s="6"/>
-      <c r="AD11" s="3"/>
+      <c r="AD11" s="6"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
@@ -1180,8 +1193,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1215,7 +1229,7 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O12" s="6" t="s">
@@ -1263,7 +1277,7 @@
       <c r="AC12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AD12" s="3" t="s">
+      <c r="AD12" s="6" t="s">
         <v>8</v>
       </c>
       <c r="AE12" s="3" t="s">
@@ -1287,8 +1301,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,7 +1339,7 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="3">
         <v>0</v>
       </c>
       <c r="O13" s="6">
@@ -1370,7 +1387,7 @@
       <c r="AC13" s="6">
         <v>0</v>
       </c>
-      <c r="AD13" s="3">
+      <c r="AD13" s="6">
         <v>0</v>
       </c>
       <c r="AE13" s="3">
@@ -1394,222 +1411,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>26900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4700</v>
       </c>
-      <c r="G14" s="3">
-        <v>18200</v>
-      </c>
       <c r="H14" s="3">
+        <v>18400</v>
+      </c>
+      <c r="I14" s="3">
         <v>3500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>15600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-13100</v>
       </c>
-      <c r="N14" s="6">
+      <c r="O14" s="6">
         <v>800</v>
       </c>
-      <c r="O14" s="6">
+      <c r="P14" s="6">
         <v>700</v>
       </c>
-      <c r="P14" s="6">
+      <c r="Q14" s="6">
         <v>6400</v>
       </c>
-      <c r="Q14" s="6">
+      <c r="R14" s="6">
         <v>2000</v>
       </c>
-      <c r="R14" s="6">
+      <c r="S14" s="6">
         <v>2400</v>
       </c>
-      <c r="S14" s="6">
+      <c r="T14" s="6">
         <v>474400</v>
       </c>
-      <c r="T14" s="6">
+      <c r="U14" s="6">
         <v>2000</v>
       </c>
-      <c r="U14" s="6">
+      <c r="V14" s="6">
         <v>8700</v>
       </c>
-      <c r="V14" s="6">
+      <c r="W14" s="6">
         <v>6700</v>
       </c>
-      <c r="W14" s="6">
+      <c r="X14" s="6">
         <v>1800</v>
       </c>
-      <c r="X14" s="6">
+      <c r="Y14" s="6">
         <v>3400</v>
       </c>
-      <c r="Y14" s="6">
+      <c r="Z14" s="6">
         <v>28800</v>
       </c>
-      <c r="Z14" s="6">
+      <c r="AA14" s="6">
         <v>6200</v>
       </c>
-      <c r="AA14" s="6">
+      <c r="AB14" s="6">
         <v>9400</v>
       </c>
-      <c r="AB14" s="6">
+      <c r="AC14" s="6">
         <v>800</v>
       </c>
-      <c r="AC14" s="6">
+      <c r="AD14" s="6">
         <v>8700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>8600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>8800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>7900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>5900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>5200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>65400</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E15" s="3">
         <v>29500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>31300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>30900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>29900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>30300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>32100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>31800</v>
       </c>
       <c r="K15" s="3">
         <v>31800</v>
       </c>
       <c r="L15" s="3">
+        <v>31800</v>
+      </c>
+      <c r="M15" s="3">
         <v>37300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>38000</v>
       </c>
-      <c r="N15" s="6">
+      <c r="O15" s="6">
         <v>38800</v>
       </c>
-      <c r="O15" s="6">
+      <c r="P15" s="6">
         <v>39800</v>
       </c>
-      <c r="P15" s="6">
+      <c r="Q15" s="6">
         <v>41400</v>
       </c>
-      <c r="Q15" s="6">
+      <c r="R15" s="6">
         <v>44700</v>
       </c>
-      <c r="R15" s="6">
+      <c r="S15" s="6">
         <v>41000</v>
       </c>
-      <c r="S15" s="6">
+      <c r="T15" s="6">
         <v>40200</v>
       </c>
-      <c r="T15" s="6">
+      <c r="U15" s="6">
         <v>40900</v>
       </c>
-      <c r="U15" s="6">
+      <c r="V15" s="6">
         <v>42000</v>
       </c>
-      <c r="V15" s="6">
+      <c r="W15" s="6">
         <v>42800</v>
       </c>
-      <c r="W15" s="6">
+      <c r="X15" s="6">
         <v>40600</v>
       </c>
-      <c r="X15" s="6">
+      <c r="Y15" s="6">
         <v>42000</v>
       </c>
-      <c r="Y15" s="6">
+      <c r="Z15" s="6">
         <v>40500</v>
       </c>
-      <c r="Z15" s="6">
+      <c r="AA15" s="6">
         <v>39500</v>
       </c>
-      <c r="AA15" s="6">
+      <c r="AB15" s="6">
         <v>38000</v>
       </c>
-      <c r="AB15" s="6">
+      <c r="AC15" s="6">
         <v>40500</v>
       </c>
-      <c r="AC15" s="6">
+      <c r="AD15" s="6">
         <v>42800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>50400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>54200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>55900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>55400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>55800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>25100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>10100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1620,7 +1646,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="6"/>
+      <c r="N16" s="3"/>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1636,7 +1662,7 @@
       <c r="AA16" s="6"/>
       <c r="AB16" s="6"/>
       <c r="AC16" s="6"/>
-      <c r="AD16" s="3"/>
+      <c r="AD16" s="6"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
@@ -1644,222 +1670,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>943100</v>
+      </c>
+      <c r="E17" s="3">
         <v>767200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>768200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>766700</v>
       </c>
-      <c r="G17" s="3">
-        <v>817300</v>
-      </c>
       <c r="H17" s="3">
+        <v>817100</v>
+      </c>
+      <c r="I17" s="3">
         <v>840900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>806900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>749200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>679300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>674200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>689600</v>
       </c>
-      <c r="N17" s="6">
+      <c r="O17" s="6">
         <v>637600</v>
       </c>
-      <c r="O17" s="6">
+      <c r="P17" s="6">
         <v>663000</v>
       </c>
-      <c r="P17" s="6">
+      <c r="Q17" s="6">
         <v>740300</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="R17" s="6">
         <v>754200</v>
       </c>
-      <c r="R17" s="6">
+      <c r="S17" s="6">
         <v>756700</v>
       </c>
-      <c r="S17" s="6">
+      <c r="T17" s="6">
         <v>1223200</v>
       </c>
-      <c r="T17" s="6">
+      <c r="U17" s="6">
         <v>734800</v>
       </c>
-      <c r="U17" s="6">
+      <c r="V17" s="6">
         <v>650800</v>
       </c>
-      <c r="V17" s="6">
+      <c r="W17" s="6">
         <v>626100</v>
       </c>
-      <c r="W17" s="6">
+      <c r="X17" s="6">
         <v>610800</v>
       </c>
-      <c r="X17" s="6">
+      <c r="Y17" s="6">
         <v>806200</v>
       </c>
-      <c r="Y17" s="6">
+      <c r="Z17" s="6">
         <v>709400</v>
       </c>
-      <c r="Z17" s="6">
+      <c r="AA17" s="6">
         <v>653400</v>
       </c>
-      <c r="AA17" s="6">
+      <c r="AB17" s="6">
         <v>707000</v>
       </c>
-      <c r="AB17" s="6">
+      <c r="AC17" s="6">
         <v>695100</v>
       </c>
-      <c r="AC17" s="6">
+      <c r="AD17" s="6">
         <v>479400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>538400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>610000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>512000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>492100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>523000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>330100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>100000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>90600</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>499700</v>
+      </c>
+      <c r="E18" s="3">
         <v>505600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>435800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>375000</v>
       </c>
-      <c r="G18" s="3">
-        <v>356200</v>
-      </c>
       <c r="H18" s="3">
+        <v>356400</v>
+      </c>
+      <c r="I18" s="3">
         <v>354100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>300700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>306500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>294700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>283000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>279100</v>
       </c>
-      <c r="N18" s="6">
+      <c r="O18" s="6">
         <v>271200</v>
       </c>
-      <c r="O18" s="6">
+      <c r="P18" s="6">
         <v>244800</v>
       </c>
-      <c r="P18" s="6">
+      <c r="Q18" s="6">
         <v>247900</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="R18" s="6">
         <v>250500</v>
       </c>
-      <c r="R18" s="6">
+      <c r="S18" s="6">
         <v>236800</v>
       </c>
-      <c r="S18" s="6">
+      <c r="T18" s="6">
         <v>-237400</v>
       </c>
-      <c r="T18" s="6">
+      <c r="U18" s="6">
         <v>239700</v>
       </c>
-      <c r="U18" s="6">
+      <c r="V18" s="6">
         <v>215600</v>
       </c>
-      <c r="V18" s="6">
+      <c r="W18" s="6">
         <v>190700</v>
       </c>
-      <c r="W18" s="6">
+      <c r="X18" s="6">
         <v>190000</v>
       </c>
-      <c r="X18" s="6">
+      <c r="Y18" s="6">
         <v>204600</v>
       </c>
-      <c r="Y18" s="6">
+      <c r="Z18" s="6">
         <v>134800</v>
       </c>
-      <c r="Z18" s="6">
+      <c r="AA18" s="6">
         <v>139300</v>
       </c>
-      <c r="AA18" s="6">
+      <c r="AB18" s="6">
         <v>161700</v>
       </c>
-      <c r="AB18" s="6">
+      <c r="AC18" s="6">
         <v>226400</v>
       </c>
-      <c r="AC18" s="6">
+      <c r="AD18" s="6">
         <v>119200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>129100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>167700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>108700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>119300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>117800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>26100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>75100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1873,7 +1906,7 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-      <c r="N19" s="6"/>
+      <c r="N19" s="3"/>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -1889,7 +1922,7 @@
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
       <c r="AC19" s="6"/>
-      <c r="AD19" s="3"/>
+      <c r="AD19" s="6"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
@@ -1897,227 +1930,234 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1900</v>
       </c>
-      <c r="N20" s="6">
+      <c r="O20" s="6">
         <v>14300</v>
       </c>
-      <c r="O20" s="6">
+      <c r="P20" s="6">
         <v>13700</v>
       </c>
-      <c r="P20" s="6">
+      <c r="Q20" s="6">
         <v>17400</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="R20" s="6">
         <v>2400</v>
       </c>
-      <c r="R20" s="6">
+      <c r="S20" s="6">
         <v>8300</v>
       </c>
-      <c r="S20" s="6">
+      <c r="T20" s="6">
         <v>-4300</v>
       </c>
-      <c r="T20" s="6">
+      <c r="U20" s="6">
         <v>-3100</v>
       </c>
-      <c r="U20" s="6">
+      <c r="V20" s="6">
         <v>6100</v>
       </c>
-      <c r="V20" s="6">
+      <c r="W20" s="6">
         <v>-5200</v>
       </c>
-      <c r="W20" s="6">
+      <c r="X20" s="6">
         <v>1600</v>
       </c>
-      <c r="X20" s="6">
+      <c r="Y20" s="6">
         <v>700</v>
       </c>
-      <c r="Y20" s="6">
+      <c r="Z20" s="6">
         <v>1800</v>
       </c>
-      <c r="Z20" s="6">
+      <c r="AA20" s="6">
         <v>33700</v>
       </c>
-      <c r="AA20" s="6">
+      <c r="AB20" s="6">
         <v>2300</v>
       </c>
-      <c r="AB20" s="6">
+      <c r="AC20" s="6">
         <v>-900</v>
       </c>
-      <c r="AC20" s="6">
+      <c r="AD20" s="6">
         <v>-5000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-8300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-13400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-11700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-7800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>5400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>528700</v>
+      </c>
+      <c r="E21" s="3">
         <v>541300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>463300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>410100</v>
       </c>
-      <c r="G21" s="3">
-        <v>384300</v>
-      </c>
       <c r="H21" s="3">
+        <v>384500</v>
+      </c>
+      <c r="I21" s="3">
         <v>388400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>333300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>341500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>329400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>324900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>315200</v>
       </c>
-      <c r="N21" s="6">
+      <c r="O21" s="6">
         <v>324300</v>
       </c>
-      <c r="O21" s="6">
+      <c r="P21" s="6">
         <v>298300</v>
       </c>
-      <c r="P21" s="6">
+      <c r="Q21" s="6">
         <v>306700</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="R21" s="6">
         <v>297600</v>
       </c>
-      <c r="R21" s="6">
+      <c r="S21" s="6">
         <v>286100</v>
       </c>
-      <c r="S21" s="6">
+      <c r="T21" s="6">
         <v>-201500</v>
       </c>
-      <c r="T21" s="6">
+      <c r="U21" s="6">
         <v>277500</v>
       </c>
-      <c r="U21" s="6">
+      <c r="V21" s="6">
         <v>263700</v>
       </c>
-      <c r="V21" s="6">
+      <c r="W21" s="6">
         <v>228300</v>
       </c>
-      <c r="W21" s="6">
+      <c r="X21" s="6">
         <v>232200</v>
       </c>
-      <c r="X21" s="6">
+      <c r="Y21" s="6">
         <v>247300</v>
       </c>
-      <c r="Y21" s="6">
+      <c r="Z21" s="6">
         <v>177100</v>
       </c>
-      <c r="Z21" s="6">
+      <c r="AA21" s="6">
         <v>212500</v>
       </c>
-      <c r="AA21" s="6">
+      <c r="AB21" s="6">
         <v>202000</v>
       </c>
-      <c r="AB21" s="6">
+      <c r="AC21" s="6">
         <v>266000</v>
       </c>
-      <c r="AC21" s="6">
+      <c r="AD21" s="6">
         <v>157000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>170200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>213600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>160000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>161300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>161900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>43400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>90600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>13300</v>
+        <v>13200</v>
       </c>
       <c r="E22" s="3">
         <v>13300</v>
@@ -2126,75 +2166,75 @@
         <v>13300</v>
       </c>
       <c r="G22" s="3">
+        <v>13300</v>
+      </c>
+      <c r="H22" s="3">
         <v>12900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>12800</v>
       </c>
       <c r="K22" s="3">
         <v>12800</v>
       </c>
       <c r="L22" s="3">
+        <v>12800</v>
+      </c>
+      <c r="M22" s="3">
         <v>13000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13200</v>
       </c>
-      <c r="N22" s="6">
+      <c r="O22" s="6">
         <v>15400</v>
       </c>
-      <c r="O22" s="6">
+      <c r="P22" s="6">
         <v>16700</v>
-      </c>
-      <c r="P22" s="6">
-        <v>17100</v>
       </c>
       <c r="Q22" s="6">
         <v>17100</v>
       </c>
       <c r="R22" s="6">
+        <v>17100</v>
+      </c>
+      <c r="S22" s="6">
         <v>16100</v>
       </c>
-      <c r="S22" s="6">
+      <c r="T22" s="6">
         <v>15100</v>
       </c>
-      <c r="T22" s="6">
+      <c r="U22" s="6">
         <v>11700</v>
       </c>
-      <c r="U22" s="6">
+      <c r="V22" s="6">
         <v>11500</v>
       </c>
-      <c r="V22" s="6">
+      <c r="W22" s="6">
         <v>11700</v>
-      </c>
-      <c r="W22" s="6">
-        <v>12400</v>
       </c>
       <c r="X22" s="6">
         <v>12400</v>
       </c>
       <c r="Y22" s="6">
+        <v>12400</v>
+      </c>
+      <c r="Z22" s="6">
         <v>13700</v>
       </c>
-      <c r="Z22" s="6">
+      <c r="AA22" s="6">
         <v>9600</v>
       </c>
-      <c r="AA22" s="6">
+      <c r="AB22" s="6">
         <v>7400</v>
       </c>
-      <c r="AB22" s="6">
+      <c r="AC22" s="6">
         <v>8000</v>
       </c>
-      <c r="AC22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD22" s="3" t="s">
+      <c r="AD22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="AE22" s="3" t="s">
@@ -2212,228 +2252,237 @@
       <c r="AI22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK22" s="3">
         <v>5500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>494700</v>
+      </c>
+      <c r="E23" s="3">
         <v>515500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>451700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>430100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>334600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>350200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>279700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>309000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>203000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>292100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>287500</v>
       </c>
-      <c r="N23" s="6">
+      <c r="O23" s="6">
         <v>270100</v>
       </c>
-      <c r="O23" s="6">
+      <c r="P23" s="6">
         <v>241800</v>
       </c>
-      <c r="P23" s="6">
+      <c r="Q23" s="6">
         <v>248200</v>
       </c>
-      <c r="Q23" s="6">
+      <c r="R23" s="6">
         <v>235800</v>
       </c>
-      <c r="R23" s="6">
+      <c r="S23" s="6">
         <v>229000</v>
       </c>
-      <c r="S23" s="6">
+      <c r="T23" s="6">
         <v>-256800</v>
       </c>
-      <c r="T23" s="6">
+      <c r="U23" s="6">
         <v>224900</v>
       </c>
-      <c r="U23" s="6">
+      <c r="V23" s="6">
         <v>210200</v>
       </c>
-      <c r="V23" s="6">
+      <c r="W23" s="6">
         <v>173800</v>
       </c>
-      <c r="W23" s="6">
+      <c r="X23" s="6">
         <v>179200</v>
       </c>
-      <c r="X23" s="6">
+      <c r="Y23" s="6">
         <v>192900</v>
       </c>
-      <c r="Y23" s="6">
+      <c r="Z23" s="6">
         <v>122900</v>
       </c>
-      <c r="Z23" s="6">
+      <c r="AA23" s="6">
         <v>163400</v>
       </c>
-      <c r="AA23" s="6">
+      <c r="AB23" s="6">
         <v>156600</v>
       </c>
-      <c r="AB23" s="6">
+      <c r="AC23" s="6">
         <v>217500</v>
       </c>
-      <c r="AC23" s="6">
+      <c r="AD23" s="6">
         <v>114200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>119800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>159400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>104100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>105900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>106100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>18300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>75000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>67300</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>141600</v>
+      </c>
+      <c r="E24" s="3">
         <v>129800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>138200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>129300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>99500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>99600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>83200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>90500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>62600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>82600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>75500</v>
       </c>
-      <c r="N24" s="6">
+      <c r="O24" s="6">
         <v>61900</v>
       </c>
-      <c r="O24" s="6">
+      <c r="P24" s="6">
         <v>74000</v>
       </c>
-      <c r="P24" s="6">
+      <c r="Q24" s="6">
         <v>74800</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="R24" s="6">
         <v>76100</v>
       </c>
-      <c r="R24" s="6">
+      <c r="S24" s="6">
         <v>78800</v>
       </c>
-      <c r="S24" s="6">
+      <c r="T24" s="6">
         <v>-72300</v>
       </c>
-      <c r="T24" s="6">
+      <c r="U24" s="6">
         <v>115300</v>
       </c>
-      <c r="U24" s="6">
+      <c r="V24" s="6">
         <v>44300</v>
       </c>
-      <c r="V24" s="6">
+      <c r="W24" s="6">
         <v>53400</v>
       </c>
-      <c r="W24" s="6">
+      <c r="X24" s="6">
         <v>73700</v>
       </c>
-      <c r="X24" s="6">
+      <c r="Y24" s="6">
         <v>55700</v>
       </c>
-      <c r="Y24" s="6">
+      <c r="Z24" s="6">
         <v>35600</v>
       </c>
-      <c r="Z24" s="6">
+      <c r="AA24" s="6">
         <v>53500</v>
       </c>
-      <c r="AA24" s="6">
+      <c r="AB24" s="6">
         <v>43000</v>
       </c>
-      <c r="AB24" s="6">
+      <c r="AC24" s="6">
         <v>60100</v>
       </c>
-      <c r="AC24" s="6">
+      <c r="AD24" s="6">
         <v>27900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>36800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>41300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>38100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>45600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>38100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>29800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2467,7 +2516,7 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="6">
+      <c r="N25" s="3">
         <v>0</v>
       </c>
       <c r="O25" s="6">
@@ -2515,7 +2564,7 @@
       <c r="AC25" s="6">
         <v>0</v>
       </c>
-      <c r="AD25" s="3">
+      <c r="AD25" s="6">
         <v>0</v>
       </c>
       <c r="AE25" s="3">
@@ -2539,222 +2588,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>353100</v>
+      </c>
+      <c r="E26" s="3">
         <v>385700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>313500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>300800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>235100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>250600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>196500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>218500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>140400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>209500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>212000</v>
       </c>
-      <c r="N26" s="6">
+      <c r="O26" s="6">
         <v>208200</v>
       </c>
-      <c r="O26" s="6">
+      <c r="P26" s="6">
         <v>167800</v>
       </c>
-      <c r="P26" s="6">
+      <c r="Q26" s="6">
         <v>173400</v>
       </c>
-      <c r="Q26" s="6">
+      <c r="R26" s="6">
         <v>159700</v>
       </c>
-      <c r="R26" s="6">
+      <c r="S26" s="6">
         <v>150200</v>
       </c>
-      <c r="S26" s="6">
+      <c r="T26" s="6">
         <v>-184500</v>
       </c>
-      <c r="T26" s="6">
+      <c r="U26" s="6">
         <v>109600</v>
       </c>
-      <c r="U26" s="6">
+      <c r="V26" s="6">
         <v>165900</v>
       </c>
-      <c r="V26" s="6">
+      <c r="W26" s="6">
         <v>120400</v>
       </c>
-      <c r="W26" s="6">
+      <c r="X26" s="6">
         <v>105500</v>
       </c>
-      <c r="X26" s="6">
+      <c r="Y26" s="6">
         <v>137200</v>
       </c>
-      <c r="Y26" s="6">
+      <c r="Z26" s="6">
         <v>87300</v>
       </c>
-      <c r="Z26" s="6">
+      <c r="AA26" s="6">
         <v>109900</v>
       </c>
-      <c r="AA26" s="6">
+      <c r="AB26" s="6">
         <v>113600</v>
       </c>
-      <c r="AB26" s="6">
+      <c r="AC26" s="6">
         <v>157400</v>
       </c>
-      <c r="AC26" s="6">
+      <c r="AD26" s="6">
         <v>86300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>83000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>118100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>66000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>60300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>68000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>15200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>45200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>40500</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>351800</v>
+      </c>
+      <c r="E27" s="3">
         <v>384100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>312200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>299300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>233900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>249400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>195600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>217400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>139700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>208300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>210800</v>
       </c>
-      <c r="N27" s="6">
+      <c r="O27" s="6">
         <v>207100</v>
       </c>
-      <c r="O27" s="6">
+      <c r="P27" s="6">
         <v>167000</v>
       </c>
-      <c r="P27" s="6">
+      <c r="Q27" s="6">
         <v>172600</v>
       </c>
-      <c r="Q27" s="6">
+      <c r="R27" s="6">
         <v>159400</v>
       </c>
-      <c r="R27" s="6">
+      <c r="S27" s="6">
         <v>149600</v>
       </c>
-      <c r="S27" s="6">
+      <c r="T27" s="6">
         <v>-184500</v>
       </c>
-      <c r="T27" s="6">
+      <c r="U27" s="6">
         <v>109200</v>
       </c>
-      <c r="U27" s="6">
+      <c r="V27" s="6">
         <v>165300</v>
       </c>
-      <c r="V27" s="6">
+      <c r="W27" s="6">
         <v>120000</v>
       </c>
-      <c r="W27" s="6">
+      <c r="X27" s="6">
         <v>105200</v>
       </c>
-      <c r="X27" s="6">
+      <c r="Y27" s="6">
         <v>136800</v>
       </c>
-      <c r="Y27" s="6">
+      <c r="Z27" s="6">
         <v>87100</v>
       </c>
-      <c r="Z27" s="6">
+      <c r="AA27" s="6">
         <v>109600</v>
       </c>
-      <c r="AA27" s="6">
+      <c r="AB27" s="6">
         <v>113300</v>
       </c>
-      <c r="AB27" s="6">
+      <c r="AC27" s="6">
         <v>157000</v>
       </c>
-      <c r="AC27" s="6">
+      <c r="AD27" s="6">
         <v>86100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>82400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>117300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>63500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>59700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>67300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>45000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>40300</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2788,7 +2846,7 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="6">
+      <c r="N28" s="3">
         <v>0</v>
       </c>
       <c r="O28" s="6">
@@ -2836,7 +2894,7 @@
       <c r="AC28" s="6">
         <v>0</v>
       </c>
-      <c r="AD28" s="3">
+      <c r="AD28" s="6">
         <v>0</v>
       </c>
       <c r="AE28" s="3">
@@ -2860,8 +2918,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2895,7 +2956,7 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="6">
+      <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="6">
@@ -2943,17 +3004,17 @@
       <c r="AC29" s="6">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="6">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>191100</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2967,8 +3028,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3002,7 +3066,7 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="6">
+      <c r="N30" s="3">
         <v>0</v>
       </c>
       <c r="O30" s="6">
@@ -3050,7 +3114,7 @@
       <c r="AC30" s="6">
         <v>0</v>
       </c>
-      <c r="AD30" s="3">
+      <c r="AD30" s="6">
         <v>0</v>
       </c>
       <c r="AE30" s="3">
@@ -3074,8 +3138,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3109,7 +3176,7 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="6">
+      <c r="N31" s="3">
         <v>0</v>
       </c>
       <c r="O31" s="6">
@@ -3157,7 +3224,7 @@
       <c r="AC31" s="6">
         <v>0</v>
       </c>
-      <c r="AD31" s="3">
+      <c r="AD31" s="6">
         <v>0</v>
       </c>
       <c r="AE31" s="3">
@@ -3181,222 +3248,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>6200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1900</v>
       </c>
-      <c r="N32" s="6">
+      <c r="O32" s="6">
         <v>-14300</v>
       </c>
-      <c r="O32" s="6">
+      <c r="P32" s="6">
         <v>-13700</v>
       </c>
-      <c r="P32" s="6">
+      <c r="Q32" s="6">
         <v>-17400</v>
       </c>
-      <c r="Q32" s="6">
+      <c r="R32" s="6">
         <v>-2400</v>
       </c>
-      <c r="R32" s="6">
+      <c r="S32" s="6">
         <v>-8300</v>
       </c>
-      <c r="S32" s="6">
+      <c r="T32" s="6">
         <v>4300</v>
       </c>
-      <c r="T32" s="6">
+      <c r="U32" s="6">
         <v>3100</v>
       </c>
-      <c r="U32" s="6">
+      <c r="V32" s="6">
         <v>-6100</v>
       </c>
-      <c r="V32" s="6">
+      <c r="W32" s="6">
         <v>5200</v>
       </c>
-      <c r="W32" s="6">
+      <c r="X32" s="6">
         <v>-1600</v>
       </c>
-      <c r="X32" s="6">
+      <c r="Y32" s="6">
         <v>-700</v>
       </c>
-      <c r="Y32" s="6">
+      <c r="Z32" s="6">
         <v>-1800</v>
       </c>
-      <c r="Z32" s="6">
+      <c r="AA32" s="6">
         <v>-33700</v>
       </c>
-      <c r="AA32" s="6">
+      <c r="AB32" s="6">
         <v>-2300</v>
       </c>
-      <c r="AB32" s="6">
+      <c r="AC32" s="6">
         <v>900</v>
       </c>
-      <c r="AC32" s="6">
+      <c r="AD32" s="6">
         <v>5000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>9300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>8300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>13400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>11700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>7800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-5400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>353100</v>
+      </c>
+      <c r="E33" s="3">
         <v>385700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>313500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>300800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>235100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>250600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>196500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>218500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>140400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>209500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>212000</v>
       </c>
-      <c r="N33" s="6">
+      <c r="O33" s="6">
         <v>207100</v>
       </c>
-      <c r="O33" s="6">
+      <c r="P33" s="6">
         <v>167000</v>
       </c>
-      <c r="P33" s="6">
+      <c r="Q33" s="6">
         <v>172600</v>
       </c>
-      <c r="Q33" s="6">
+      <c r="R33" s="6">
         <v>159400</v>
       </c>
-      <c r="R33" s="6">
+      <c r="S33" s="6">
         <v>149600</v>
       </c>
-      <c r="S33" s="6">
+      <c r="T33" s="6">
         <v>-184500</v>
       </c>
-      <c r="T33" s="6">
+      <c r="U33" s="6">
         <v>109200</v>
       </c>
-      <c r="U33" s="6">
+      <c r="V33" s="6">
         <v>165300</v>
       </c>
-      <c r="V33" s="6">
+      <c r="W33" s="6">
         <v>120000</v>
       </c>
-      <c r="W33" s="6">
+      <c r="X33" s="6">
         <v>105200</v>
       </c>
-      <c r="X33" s="6">
+      <c r="Y33" s="6">
         <v>136800</v>
       </c>
-      <c r="Y33" s="6">
+      <c r="Z33" s="6">
         <v>87100</v>
       </c>
-      <c r="Z33" s="6">
+      <c r="AA33" s="6">
         <v>109600</v>
       </c>
-      <c r="AA33" s="6">
+      <c r="AB33" s="6">
         <v>113300</v>
       </c>
-      <c r="AB33" s="6">
+      <c r="AC33" s="6">
         <v>157000</v>
       </c>
-      <c r="AC33" s="6">
+      <c r="AD33" s="6">
         <v>86100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>82400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>117300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>254600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>59700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>67300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>45000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>40300</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3430,7 +3506,7 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="6">
+      <c r="N34" s="3">
         <v>0</v>
       </c>
       <c r="O34" s="6">
@@ -3478,7 +3554,7 @@
       <c r="AC34" s="6">
         <v>0</v>
       </c>
-      <c r="AD34" s="3">
+      <c r="AD34" s="6">
         <v>0</v>
       </c>
       <c r="AE34" s="3">
@@ -3502,227 +3578,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>353100</v>
+      </c>
+      <c r="E35" s="3">
         <v>385700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>313500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>300800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>235100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>250600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>196500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>218500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>140400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>209500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>212000</v>
       </c>
-      <c r="N35" s="6">
+      <c r="O35" s="6">
         <v>207100</v>
       </c>
-      <c r="O35" s="6">
+      <c r="P35" s="6">
         <v>167000</v>
       </c>
-      <c r="P35" s="6">
+      <c r="Q35" s="6">
         <v>172600</v>
       </c>
-      <c r="Q35" s="6">
+      <c r="R35" s="6">
         <v>159400</v>
       </c>
-      <c r="R35" s="6">
+      <c r="S35" s="6">
         <v>149600</v>
       </c>
-      <c r="S35" s="6">
+      <c r="T35" s="6">
         <v>-184500</v>
       </c>
-      <c r="T35" s="6">
+      <c r="U35" s="6">
         <v>109200</v>
       </c>
-      <c r="U35" s="6">
+      <c r="V35" s="6">
         <v>165300</v>
       </c>
-      <c r="V35" s="6">
+      <c r="W35" s="6">
         <v>120000</v>
       </c>
-      <c r="W35" s="6">
+      <c r="X35" s="6">
         <v>105200</v>
       </c>
-      <c r="X35" s="6">
+      <c r="Y35" s="6">
         <v>136800</v>
       </c>
-      <c r="Y35" s="6">
+      <c r="Z35" s="6">
         <v>87100</v>
       </c>
-      <c r="Z35" s="6">
+      <c r="AA35" s="6">
         <v>109600</v>
       </c>
-      <c r="AA35" s="6">
+      <c r="AB35" s="6">
         <v>113300</v>
       </c>
-      <c r="AB35" s="6">
+      <c r="AC35" s="6">
         <v>157000</v>
       </c>
-      <c r="AC35" s="6">
+      <c r="AD35" s="6">
         <v>86100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>82400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>117300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>254600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>59700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>67300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>45000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>40300</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="5">
+      <c r="O38" s="5">
         <v>45199</v>
       </c>
-      <c r="O38" s="5">
+      <c r="P38" s="5">
         <v>45107</v>
       </c>
-      <c r="P38" s="5">
+      <c r="Q38" s="5">
         <v>45016</v>
       </c>
-      <c r="Q38" s="5">
+      <c r="R38" s="5">
         <v>44926</v>
       </c>
-      <c r="R38" s="5">
+      <c r="S38" s="5">
         <v>44834</v>
       </c>
-      <c r="S38" s="5">
+      <c r="T38" s="5">
         <v>44742</v>
       </c>
-      <c r="T38" s="5">
+      <c r="U38" s="5">
         <v>44651</v>
       </c>
-      <c r="U38" s="5">
+      <c r="V38" s="5">
         <v>44561</v>
       </c>
-      <c r="V38" s="5">
+      <c r="W38" s="5">
         <v>44469</v>
       </c>
-      <c r="W38" s="5">
+      <c r="X38" s="5">
         <v>44377</v>
       </c>
-      <c r="X38" s="5">
+      <c r="Y38" s="5">
         <v>44286</v>
       </c>
-      <c r="Y38" s="5">
+      <c r="Z38" s="5">
         <v>44196</v>
       </c>
-      <c r="Z38" s="5">
+      <c r="AA38" s="5">
         <v>44104</v>
       </c>
-      <c r="AA38" s="5">
+      <c r="AB38" s="5">
         <v>44012</v>
       </c>
-      <c r="AB38" s="5">
+      <c r="AC38" s="5">
         <v>43921</v>
       </c>
-      <c r="AC38" s="5">
+      <c r="AD38" s="5">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3736,7 +3821,7 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-      <c r="N39" s="6"/>
+      <c r="N39" s="3"/>
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
@@ -3752,7 +3837,7 @@
       <c r="AA39" s="6"/>
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
-      <c r="AD39" s="3"/>
+      <c r="AD39" s="6"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
@@ -3760,8 +3845,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3775,7 +3861,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-      <c r="N40" s="6"/>
+      <c r="N40" s="3"/>
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
@@ -3791,7 +3877,7 @@
       <c r="AA40" s="6"/>
       <c r="AB40" s="6"/>
       <c r="AC40" s="6"/>
-      <c r="AD40" s="3"/>
+      <c r="AD40" s="6"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
@@ -3799,329 +3885,339 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2280000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2135700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2216500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1496700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1256300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1047200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>920300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>763200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>614600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>536300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>543200</v>
       </c>
-      <c r="N41" s="6">
+      <c r="O41" s="6">
         <v>403100</v>
       </c>
-      <c r="O41" s="6">
+      <c r="P41" s="6">
         <v>413600</v>
       </c>
-      <c r="P41" s="6">
+      <c r="Q41" s="6">
         <v>435600</v>
       </c>
-      <c r="Q41" s="6">
+      <c r="R41" s="6">
         <v>432700</v>
       </c>
-      <c r="R41" s="6">
+      <c r="S41" s="6">
         <v>353300</v>
       </c>
-      <c r="S41" s="6">
+      <c r="T41" s="6">
         <v>373300</v>
       </c>
-      <c r="T41" s="6">
+      <c r="U41" s="6">
         <v>659400</v>
       </c>
-      <c r="U41" s="6">
+      <c r="V41" s="6">
         <v>341900</v>
       </c>
-      <c r="V41" s="6">
+      <c r="W41" s="6">
         <v>392400</v>
       </c>
-      <c r="W41" s="6">
+      <c r="X41" s="6">
         <v>450900</v>
       </c>
-      <c r="X41" s="6">
+      <c r="Y41" s="6">
         <v>263300</v>
       </c>
-      <c r="Y41" s="6">
+      <c r="Z41" s="6">
         <v>245400</v>
       </c>
-      <c r="Z41" s="6">
+      <c r="AA41" s="6">
         <v>212700</v>
       </c>
-      <c r="AA41" s="6">
+      <c r="AB41" s="6">
         <v>210100</v>
       </c>
-      <c r="AB41" s="6">
+      <c r="AC41" s="6">
         <v>165200</v>
       </c>
-      <c r="AC41" s="6">
+      <c r="AD41" s="6">
         <v>229300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>140000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>166300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>143500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>124800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>148600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>153300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>97300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>72800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E42" s="3">
         <v>500</v>
-      </c>
-      <c r="E42" s="3">
-        <v>300</v>
       </c>
       <c r="F42" s="3">
         <v>300</v>
       </c>
       <c r="G42" s="3">
+        <v>300</v>
+      </c>
+      <c r="H42" s="3">
         <v>176600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>78000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>70000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>39400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>83700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>58800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>57500</v>
       </c>
-      <c r="N42" s="6">
+      <c r="O42" s="6">
         <v>34000</v>
       </c>
-      <c r="O42" s="6">
+      <c r="P42" s="6">
         <v>103700</v>
       </c>
-      <c r="P42" s="6">
+      <c r="Q42" s="6">
         <v>80200</v>
       </c>
-      <c r="Q42" s="6">
+      <c r="R42" s="6">
         <v>91700</v>
       </c>
-      <c r="R42" s="6">
+      <c r="S42" s="6">
         <v>27400</v>
       </c>
-      <c r="S42" s="6">
+      <c r="T42" s="6">
         <v>68500</v>
       </c>
-      <c r="T42" s="6">
+      <c r="U42" s="6">
         <v>48700</v>
       </c>
-      <c r="U42" s="6">
+      <c r="V42" s="6">
         <v>37100</v>
       </c>
-      <c r="V42" s="6">
+      <c r="W42" s="6">
         <v>26700</v>
       </c>
-      <c r="W42" s="6">
+      <c r="X42" s="6">
         <v>118700</v>
       </c>
-      <c r="X42" s="6">
+      <c r="Y42" s="6">
         <v>95500</v>
       </c>
-      <c r="Y42" s="6">
+      <c r="Z42" s="6">
         <v>92400</v>
       </c>
-      <c r="Z42" s="6">
+      <c r="AA42" s="6">
         <v>22800</v>
       </c>
-      <c r="AA42" s="6">
+      <c r="AB42" s="6">
         <v>176500</v>
       </c>
-      <c r="AB42" s="6">
+      <c r="AC42" s="6">
         <v>43600</v>
       </c>
-      <c r="AC42" s="6">
+      <c r="AD42" s="6">
         <v>71000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>131800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>64000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>47300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>110400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>41300</v>
-      </c>
-      <c r="AJ42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>647500</v>
+      </c>
+      <c r="E43" s="3">
         <v>514600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>459300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>471000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>484900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>494400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>518400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>423300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>407600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>377000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>411800</v>
       </c>
-      <c r="N43" s="6">
+      <c r="O43" s="6">
         <v>419500</v>
       </c>
-      <c r="O43" s="6">
+      <c r="P43" s="6">
         <v>401600</v>
       </c>
-      <c r="P43" s="6">
+      <c r="Q43" s="6">
         <v>397900</v>
       </c>
-      <c r="Q43" s="6">
+      <c r="R43" s="6">
         <v>418100</v>
       </c>
-      <c r="R43" s="6">
+      <c r="S43" s="6">
         <v>419700</v>
       </c>
-      <c r="S43" s="6">
+      <c r="T43" s="6">
         <v>442400</v>
       </c>
-      <c r="T43" s="6">
+      <c r="U43" s="6">
         <v>380300</v>
       </c>
-      <c r="U43" s="6">
+      <c r="V43" s="6">
         <v>369600</v>
       </c>
-      <c r="V43" s="6">
+      <c r="W43" s="6">
         <v>372500</v>
       </c>
-      <c r="W43" s="6">
+      <c r="X43" s="6">
         <v>372800</v>
       </c>
-      <c r="X43" s="6">
+      <c r="Y43" s="6">
         <v>374800</v>
       </c>
-      <c r="Y43" s="6">
+      <c r="Z43" s="6">
         <v>390400</v>
       </c>
-      <c r="Z43" s="6">
+      <c r="AA43" s="6">
         <v>341600</v>
       </c>
-      <c r="AA43" s="6">
+      <c r="AB43" s="6">
         <v>376800</v>
       </c>
-      <c r="AB43" s="6">
+      <c r="AC43" s="6">
         <v>408000</v>
       </c>
-      <c r="AC43" s="6">
+      <c r="AD43" s="6">
         <v>291500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>252200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>268400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>217300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>195800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>231300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>233300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>69900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>61100</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4155,8 +4251,8 @@
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N44" s="6">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O44" s="6">
         <v>0</v>
@@ -4203,7 +4299,7 @@
       <c r="AC44" s="6">
         <v>0</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AD44" s="6">
         <v>0</v>
       </c>
       <c r="AE44" s="3">
@@ -4227,543 +4323,561 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>357900</v>
+      </c>
+      <c r="E45" s="3">
         <v>96200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1711200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1187300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1239300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>123400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>970400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>58600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>64600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>173200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>961700</v>
       </c>
-      <c r="N45" s="6">
+      <c r="O45" s="6">
         <v>1421300</v>
       </c>
-      <c r="O45" s="6">
+      <c r="P45" s="6">
         <v>825400</v>
       </c>
-      <c r="P45" s="6">
+      <c r="Q45" s="6">
         <v>1544400</v>
       </c>
-      <c r="Q45" s="6">
+      <c r="R45" s="6">
         <v>613500</v>
       </c>
-      <c r="R45" s="6">
+      <c r="S45" s="6">
         <v>1096600</v>
       </c>
-      <c r="S45" s="6">
+      <c r="T45" s="6">
         <v>1048600</v>
       </c>
-      <c r="T45" s="6">
+      <c r="U45" s="6">
         <v>1846800</v>
       </c>
-      <c r="U45" s="6">
+      <c r="V45" s="6">
         <v>782700</v>
       </c>
-      <c r="V45" s="6">
+      <c r="W45" s="6">
         <v>1707200</v>
       </c>
-      <c r="W45" s="6">
+      <c r="X45" s="6">
         <v>1238400</v>
       </c>
-      <c r="X45" s="6">
+      <c r="Y45" s="6">
         <v>1299500</v>
       </c>
-      <c r="Y45" s="6">
+      <c r="Z45" s="6">
         <v>838600</v>
       </c>
-      <c r="Z45" s="6">
+      <c r="AA45" s="6">
         <v>805200</v>
       </c>
-      <c r="AA45" s="6">
+      <c r="AB45" s="6">
         <v>17800</v>
       </c>
-      <c r="AB45" s="6">
+      <c r="AC45" s="6">
         <v>15300</v>
       </c>
-      <c r="AC45" s="6">
+      <c r="AD45" s="6">
         <v>15800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>60000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>13600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>26600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>51300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>29400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>27800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>67800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5926800</v>
+      </c>
+      <c r="E46" s="3">
         <v>6224100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4421400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3742000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3742900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3361900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2479100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3318000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3899500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2675100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1979300</v>
       </c>
-      <c r="N46" s="6">
+      <c r="O46" s="6">
         <v>2277900</v>
       </c>
-      <c r="O46" s="6">
+      <c r="P46" s="6">
         <v>1744300</v>
       </c>
-      <c r="P46" s="6">
+      <c r="Q46" s="6">
         <v>2458100</v>
       </c>
-      <c r="Q46" s="6">
+      <c r="R46" s="6">
         <v>1556000</v>
       </c>
-      <c r="R46" s="6">
+      <c r="S46" s="6">
         <v>1897000</v>
       </c>
-      <c r="S46" s="6">
+      <c r="T46" s="6">
         <v>1932800</v>
       </c>
-      <c r="T46" s="6">
+      <c r="U46" s="6">
         <v>2935200</v>
       </c>
-      <c r="U46" s="6">
+      <c r="V46" s="6">
         <v>1531300</v>
       </c>
-      <c r="V46" s="6">
+      <c r="W46" s="6">
         <v>2498800</v>
       </c>
-      <c r="W46" s="6">
+      <c r="X46" s="6">
         <v>2180800</v>
       </c>
-      <c r="X46" s="6">
+      <c r="Y46" s="6">
         <v>2033100</v>
       </c>
-      <c r="Y46" s="6">
+      <c r="Z46" s="6">
         <v>1566800</v>
       </c>
-      <c r="Z46" s="6">
+      <c r="AA46" s="6">
         <v>1382300</v>
       </c>
-      <c r="AA46" s="6">
+      <c r="AB46" s="6">
         <v>781200</v>
       </c>
-      <c r="AB46" s="6">
+      <c r="AC46" s="6">
         <v>632100</v>
       </c>
-      <c r="AC46" s="6">
+      <c r="AD46" s="6">
         <v>607600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>584000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>512300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>434700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>374300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>519700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>455700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>235000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>206600</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E47" s="3">
         <v>31400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>32400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>430200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>379600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>383300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>383700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>358100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>359500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>361800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>345300</v>
       </c>
-      <c r="N47" s="6">
+      <c r="O47" s="6">
         <v>473700</v>
       </c>
-      <c r="O47" s="6">
+      <c r="P47" s="6">
         <v>416200</v>
       </c>
-      <c r="P47" s="6">
+      <c r="Q47" s="6">
         <v>382100</v>
       </c>
-      <c r="Q47" s="6">
+      <c r="R47" s="6">
         <v>253200</v>
       </c>
-      <c r="R47" s="6">
+      <c r="S47" s="6">
         <v>253600</v>
       </c>
-      <c r="S47" s="6">
+      <c r="T47" s="6">
         <v>243500</v>
       </c>
-      <c r="T47" s="6">
+      <c r="U47" s="6">
         <v>244500</v>
       </c>
-      <c r="U47" s="6">
+      <c r="V47" s="6">
         <v>245800</v>
       </c>
-      <c r="V47" s="6">
+      <c r="W47" s="6">
         <v>36000</v>
       </c>
-      <c r="W47" s="6">
+      <c r="X47" s="6">
         <v>41100</v>
       </c>
-      <c r="X47" s="6">
+      <c r="Y47" s="6">
         <v>40700</v>
       </c>
-      <c r="Y47" s="6">
+      <c r="Z47" s="6">
         <v>42700</v>
       </c>
-      <c r="Z47" s="6">
+      <c r="AA47" s="6">
         <v>53200</v>
       </c>
-      <c r="AA47" s="6">
+      <c r="AB47" s="6">
         <v>61300</v>
       </c>
-      <c r="AB47" s="6">
+      <c r="AC47" s="6">
         <v>62300</v>
       </c>
-      <c r="AC47" s="6">
+      <c r="AD47" s="6">
         <v>61200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>88700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>85000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>82700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>83200</v>
-      </c>
-      <c r="AH47" s="3">
-        <v>82000</v>
       </c>
       <c r="AI47" s="3">
         <v>82000</v>
       </c>
       <c r="AJ47" s="3">
+        <v>82000</v>
+      </c>
+      <c r="AK47" s="3">
         <v>72900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>73500</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>238300</v>
+      </c>
+      <c r="E48" s="3">
         <v>242500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>244100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>242200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>250100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>244900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>242500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>239400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>230400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>236600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>245800</v>
       </c>
-      <c r="N48" s="6">
+      <c r="O48" s="6">
         <v>217500</v>
       </c>
-      <c r="O48" s="6">
+      <c r="P48" s="6">
         <v>223500</v>
       </c>
-      <c r="P48" s="6">
+      <c r="Q48" s="6">
         <v>224500</v>
       </c>
-      <c r="Q48" s="6">
+      <c r="R48" s="6">
         <v>222200</v>
       </c>
-      <c r="R48" s="6">
+      <c r="S48" s="6">
         <v>222300</v>
       </c>
-      <c r="S48" s="6">
+      <c r="T48" s="6">
         <v>234600</v>
       </c>
-      <c r="T48" s="6">
+      <c r="U48" s="6">
         <v>231500</v>
       </c>
-      <c r="U48" s="6">
+      <c r="V48" s="6">
         <v>217600</v>
       </c>
-      <c r="V48" s="6">
+      <c r="W48" s="6">
         <v>218800</v>
       </c>
-      <c r="W48" s="6">
+      <c r="X48" s="6">
         <v>211600</v>
       </c>
-      <c r="X48" s="6">
+      <c r="Y48" s="6">
         <v>191900</v>
       </c>
-      <c r="Y48" s="6">
+      <c r="Z48" s="6">
         <v>193600</v>
       </c>
-      <c r="Z48" s="6">
+      <c r="AA48" s="6">
         <v>198700</v>
       </c>
-      <c r="AA48" s="6">
+      <c r="AB48" s="6">
         <v>193400</v>
       </c>
-      <c r="AB48" s="6">
+      <c r="AC48" s="6">
         <v>184700</v>
       </c>
-      <c r="AC48" s="6">
+      <c r="AD48" s="6">
         <v>100400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>70300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>79100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>78800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>82100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>80500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>79500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>60800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4300000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4465300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4494800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4532300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4566500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4549700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4547900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4622700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4595800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4701800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4745400</v>
       </c>
-      <c r="N49" s="6">
+      <c r="O49" s="6">
         <v>4734300</v>
       </c>
-      <c r="O49" s="6">
+      <c r="P49" s="6">
         <v>4791400</v>
       </c>
-      <c r="P49" s="6">
+      <c r="Q49" s="6">
         <v>4817500</v>
       </c>
-      <c r="Q49" s="6">
+      <c r="R49" s="6">
         <v>4839900</v>
       </c>
-      <c r="R49" s="6">
+      <c r="S49" s="6">
         <v>4819900</v>
       </c>
-      <c r="S49" s="6">
+      <c r="T49" s="6">
         <v>4964500</v>
       </c>
-      <c r="T49" s="6">
+      <c r="U49" s="6">
         <v>4683900</v>
       </c>
-      <c r="U49" s="6">
+      <c r="V49" s="6">
         <v>4732500</v>
       </c>
-      <c r="V49" s="6">
+      <c r="W49" s="6">
         <v>4764700</v>
       </c>
-      <c r="W49" s="6">
+      <c r="X49" s="6">
         <v>4607900</v>
       </c>
-      <c r="X49" s="6">
+      <c r="Y49" s="6">
         <v>4633700</v>
       </c>
-      <c r="Y49" s="6">
+      <c r="Z49" s="6">
         <v>4661600</v>
       </c>
-      <c r="Z49" s="6">
+      <c r="AA49" s="6">
         <v>4397000</v>
       </c>
-      <c r="AA49" s="6">
+      <c r="AB49" s="6">
         <v>4283400</v>
       </c>
-      <c r="AB49" s="6">
+      <c r="AC49" s="6">
         <v>4309200</v>
       </c>
-      <c r="AC49" s="6">
+      <c r="AD49" s="6">
         <v>4301700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4551800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4630800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4650600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4674500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4702300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4718800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>98100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>96500</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4797,7 +4911,7 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="6">
+      <c r="N50" s="3">
         <v>0</v>
       </c>
       <c r="O50" s="6">
@@ -4845,7 +4959,7 @@
       <c r="AC50" s="6">
         <v>0</v>
       </c>
-      <c r="AD50" s="3">
+      <c r="AD50" s="6">
         <v>0</v>
       </c>
       <c r="AE50" s="3">
@@ -4869,8 +4983,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4904,7 +5021,7 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="6">
+      <c r="N51" s="3">
         <v>0</v>
       </c>
       <c r="O51" s="6">
@@ -4952,7 +5069,7 @@
       <c r="AC51" s="6">
         <v>0</v>
       </c>
-      <c r="AD51" s="3">
+      <c r="AD51" s="6">
         <v>0</v>
       </c>
       <c r="AE51" s="3">
@@ -4976,115 +5093,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E52" s="3">
         <v>10100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>34200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>34800</v>
       </c>
-      <c r="N52" s="6">
+      <c r="O52" s="6">
         <v>29100</v>
       </c>
-      <c r="O52" s="6">
+      <c r="P52" s="6">
         <v>20500</v>
       </c>
-      <c r="P52" s="6">
+      <c r="Q52" s="6">
         <v>21300</v>
       </c>
-      <c r="Q52" s="6">
+      <c r="R52" s="6">
         <v>127600</v>
       </c>
-      <c r="R52" s="6">
+      <c r="S52" s="6">
         <v>104600</v>
       </c>
-      <c r="S52" s="6">
+      <c r="T52" s="6">
         <v>100700</v>
       </c>
-      <c r="T52" s="6">
+      <c r="U52" s="6">
         <v>103000</v>
       </c>
-      <c r="U52" s="6">
+      <c r="V52" s="6">
         <v>87300</v>
       </c>
-      <c r="V52" s="6">
+      <c r="W52" s="6">
         <v>64400</v>
       </c>
-      <c r="W52" s="6">
+      <c r="X52" s="6">
         <v>55100</v>
       </c>
-      <c r="X52" s="6">
+      <c r="Y52" s="6">
         <v>58700</v>
       </c>
-      <c r="Y52" s="6">
+      <c r="Z52" s="6">
         <v>51800</v>
       </c>
-      <c r="Z52" s="6">
+      <c r="AA52" s="6">
         <v>45600</v>
       </c>
-      <c r="AA52" s="6">
+      <c r="AB52" s="6">
         <v>47000</v>
       </c>
-      <c r="AB52" s="6">
+      <c r="AC52" s="6">
         <v>49200</v>
       </c>
-      <c r="AC52" s="6">
+      <c r="AD52" s="6">
         <v>43000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>22100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>21000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>18900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>14000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>11100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9700</v>
       </c>
-      <c r="AK52" s="3" t="s">
+      <c r="AL52" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5118,7 +5241,7 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="6">
+      <c r="N53" s="3">
         <v>0</v>
       </c>
       <c r="O53" s="6">
@@ -5166,7 +5289,7 @@
       <c r="AC53" s="6">
         <v>0</v>
       </c>
-      <c r="AD53" s="3">
+      <c r="AD53" s="6">
         <v>0</v>
       </c>
       <c r="AE53" s="3">
@@ -5190,115 +5313,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10609300</v>
+      </c>
+      <c r="E54" s="3">
         <v>11070600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9305300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9068600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9048300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8667300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7789100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8711500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9255600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8152100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7487500</v>
       </c>
-      <c r="N54" s="6">
+      <c r="O54" s="6">
         <v>7732500</v>
       </c>
-      <c r="O54" s="6">
+      <c r="P54" s="6">
         <v>7195900</v>
       </c>
-      <c r="P54" s="6">
+      <c r="Q54" s="6">
         <v>7903500</v>
       </c>
-      <c r="Q54" s="6">
+      <c r="R54" s="6">
         <v>6998900</v>
       </c>
-      <c r="R54" s="6">
+      <c r="S54" s="6">
         <v>7297400</v>
       </c>
-      <c r="S54" s="6">
+      <c r="T54" s="6">
         <v>7476100</v>
       </c>
-      <c r="T54" s="6">
+      <c r="U54" s="6">
         <v>8198100</v>
       </c>
-      <c r="U54" s="6">
+      <c r="V54" s="6">
         <v>6814500</v>
       </c>
-      <c r="V54" s="6">
+      <c r="W54" s="6">
         <v>7582700</v>
       </c>
-      <c r="W54" s="6">
+      <c r="X54" s="6">
         <v>7096500</v>
       </c>
-      <c r="X54" s="6">
+      <c r="Y54" s="6">
         <v>6958100</v>
       </c>
-      <c r="Y54" s="6">
+      <c r="Z54" s="6">
         <v>6516500</v>
       </c>
-      <c r="Z54" s="6">
+      <c r="AA54" s="6">
         <v>6076800</v>
       </c>
-      <c r="AA54" s="6">
+      <c r="AB54" s="6">
         <v>5366300</v>
       </c>
-      <c r="AB54" s="6">
+      <c r="AC54" s="6">
         <v>5237500</v>
       </c>
-      <c r="AC54" s="6">
+      <c r="AD54" s="6">
         <v>5113900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5316900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5328200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5265700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5228100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5395600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5345100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>476600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>441300</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5312,7 +5441,7 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-      <c r="N55" s="6"/>
+      <c r="N55" s="3"/>
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
       <c r="Q55" s="6"/>
@@ -5328,7 +5457,7 @@
       <c r="AA55" s="6"/>
       <c r="AB55" s="6"/>
       <c r="AC55" s="6"/>
-      <c r="AD55" s="3"/>
+      <c r="AD55" s="6"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
@@ -5336,8 +5465,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5351,7 +5481,7 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-      <c r="N56" s="6"/>
+      <c r="N56" s="3"/>
       <c r="O56" s="6"/>
       <c r="P56" s="6"/>
       <c r="Q56" s="6"/>
@@ -5367,7 +5497,7 @@
       <c r="AA56" s="6"/>
       <c r="AB56" s="6"/>
       <c r="AC56" s="6"/>
-      <c r="AD56" s="3"/>
+      <c r="AD56" s="6"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
@@ -5375,162 +5505,166 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E57" s="3">
         <v>19400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>22600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24700</v>
       </c>
-      <c r="N57" s="6">
+      <c r="O57" s="6">
         <v>13500</v>
       </c>
-      <c r="O57" s="6">
+      <c r="P57" s="6">
         <v>33100</v>
       </c>
-      <c r="P57" s="6">
+      <c r="Q57" s="6">
         <v>126100</v>
       </c>
-      <c r="Q57" s="6">
+      <c r="R57" s="6">
         <v>117900</v>
       </c>
-      <c r="R57" s="6">
+      <c r="S57" s="6">
         <v>21300</v>
       </c>
-      <c r="S57" s="6">
+      <c r="T57" s="6">
         <v>35200</v>
       </c>
-      <c r="T57" s="6">
+      <c r="U57" s="6">
         <v>21200</v>
       </c>
-      <c r="U57" s="6">
+      <c r="V57" s="6">
         <v>19500</v>
       </c>
-      <c r="V57" s="6">
+      <c r="W57" s="6">
         <v>18700</v>
       </c>
-      <c r="W57" s="6">
+      <c r="X57" s="6">
         <v>12600</v>
       </c>
-      <c r="X57" s="6">
+      <c r="Y57" s="6">
         <v>11200</v>
       </c>
-      <c r="Y57" s="6">
+      <c r="Z57" s="6">
         <v>28500</v>
       </c>
-      <c r="Z57" s="6">
+      <c r="AA57" s="6">
         <v>15900</v>
       </c>
-      <c r="AA57" s="6">
+      <c r="AB57" s="6">
         <v>12200</v>
       </c>
-      <c r="AB57" s="6">
+      <c r="AC57" s="6">
         <v>9200</v>
       </c>
-      <c r="AC57" s="6">
+      <c r="AD57" s="6">
         <v>21000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>48700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>43200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>38900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>54900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>51400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>674600</v>
+      </c>
+      <c r="E58" s="3">
         <v>676100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>26900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>25100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>25000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>21000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20800</v>
       </c>
-      <c r="N58" s="6">
+      <c r="O58" s="6">
         <v>74900</v>
       </c>
-      <c r="O58" s="6">
+      <c r="P58" s="6">
         <v>164900</v>
       </c>
-      <c r="P58" s="6">
+      <c r="Q58" s="6">
         <v>304800</v>
       </c>
-      <c r="Q58" s="6">
+      <c r="R58" s="6">
         <v>304700</v>
-      </c>
-      <c r="R58" s="6" t="s">
-        <v>8</v>
       </c>
       <c r="S58" s="6" t="s">
         <v>8</v>
@@ -5538,8 +5672,8 @@
       <c r="T58" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="6">
-        <v>0</v>
+      <c r="U58" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="6">
         <v>0</v>
@@ -5548,28 +5682,28 @@
         <v>0</v>
       </c>
       <c r="X58" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="6">
         <v>49000</v>
       </c>
-      <c r="Y58" s="6">
+      <c r="Z58" s="6">
         <v>68700</v>
       </c>
-      <c r="Z58" s="6">
+      <c r="AA58" s="6">
         <v>70000</v>
-      </c>
-      <c r="AA58" s="6" t="s">
-        <v>8</v>
       </c>
       <c r="AB58" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AC58" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AC58" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
         <v>299500</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
@@ -5589,436 +5723,451 @@
       <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2751100</v>
+      </c>
+      <c r="E59" s="3">
         <v>3514500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1992700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1796200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2049500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1799000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1035600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2086400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2872700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1711600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1053000</v>
       </c>
-      <c r="N59" s="6">
+      <c r="O59" s="6">
         <v>1761100</v>
       </c>
-      <c r="O59" s="6">
+      <c r="P59" s="6">
         <v>1270100</v>
       </c>
-      <c r="P59" s="6">
+      <c r="Q59" s="6">
         <v>1872600</v>
       </c>
-      <c r="Q59" s="6">
+      <c r="R59" s="6">
         <v>1054600</v>
       </c>
-      <c r="R59" s="6">
+      <c r="S59" s="6">
         <v>1523900</v>
       </c>
-      <c r="S59" s="6">
+      <c r="T59" s="6">
         <v>1564400</v>
       </c>
-      <c r="T59" s="6">
+      <c r="U59" s="6">
         <v>2319900</v>
       </c>
-      <c r="U59" s="6">
+      <c r="V59" s="6">
         <v>1149800</v>
       </c>
-      <c r="V59" s="6">
+      <c r="W59" s="6">
         <v>1999000</v>
       </c>
-      <c r="W59" s="6">
+      <c r="X59" s="6">
         <v>1591400</v>
       </c>
-      <c r="X59" s="6">
+      <c r="Y59" s="6">
         <v>1633900</v>
       </c>
-      <c r="Y59" s="6">
+      <c r="Z59" s="6">
         <v>1216100</v>
       </c>
-      <c r="Z59" s="6">
+      <c r="AA59" s="6">
         <v>1042400</v>
       </c>
-      <c r="AA59" s="6">
+      <c r="AB59" s="6">
         <v>484300</v>
       </c>
-      <c r="AB59" s="6">
+      <c r="AC59" s="6">
         <v>348900</v>
       </c>
-      <c r="AC59" s="6">
+      <c r="AD59" s="6">
         <v>260600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>369300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>335600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>290800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>199100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>321400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>209500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>83400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3786500</v>
+      </c>
+      <c r="E60" s="3">
         <v>4493600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2362300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2178700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2386600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2097900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1395200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2389800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3158900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2007000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1383400</v>
       </c>
-      <c r="N60" s="6">
+      <c r="O60" s="6">
         <v>1849500</v>
       </c>
-      <c r="O60" s="6">
+      <c r="P60" s="6">
         <v>1468100</v>
       </c>
-      <c r="P60" s="6">
+      <c r="Q60" s="6">
         <v>2303500</v>
       </c>
-      <c r="Q60" s="6">
+      <c r="R60" s="6">
         <v>1477200</v>
       </c>
-      <c r="R60" s="6">
+      <c r="S60" s="6">
         <v>1545200</v>
       </c>
-      <c r="S60" s="6">
+      <c r="T60" s="6">
         <v>1599600</v>
       </c>
-      <c r="T60" s="6">
+      <c r="U60" s="6">
         <v>2341100</v>
       </c>
-      <c r="U60" s="6">
+      <c r="V60" s="6">
         <v>1169300</v>
       </c>
-      <c r="V60" s="6">
+      <c r="W60" s="6">
         <v>2017700</v>
       </c>
-      <c r="W60" s="6">
+      <c r="X60" s="6">
         <v>1604000</v>
       </c>
-      <c r="X60" s="6">
+      <c r="Y60" s="6">
         <v>1694100</v>
       </c>
-      <c r="Y60" s="6">
+      <c r="Z60" s="6">
         <v>1313300</v>
       </c>
-      <c r="Z60" s="6">
+      <c r="AA60" s="6">
         <v>1128300</v>
       </c>
-      <c r="AA60" s="6">
+      <c r="AB60" s="6">
         <v>496500</v>
       </c>
-      <c r="AB60" s="6">
+      <c r="AC60" s="6">
         <v>358100</v>
       </c>
-      <c r="AC60" s="6">
+      <c r="AD60" s="6">
         <v>281600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>679900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>384300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>334000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>238000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>376300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>260900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>89800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>905700</v>
+      </c>
+      <c r="E61" s="3">
         <v>908500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1563800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1569600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1575800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1579500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1579400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1584500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1566400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1583900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1590000</v>
       </c>
-      <c r="N61" s="6">
+      <c r="O61" s="6">
         <v>1438700</v>
       </c>
-      <c r="O61" s="6">
+      <c r="P61" s="6">
         <v>1438200</v>
       </c>
-      <c r="P61" s="6">
+      <c r="Q61" s="6">
         <v>1437800</v>
       </c>
-      <c r="Q61" s="6">
+      <c r="R61" s="6">
         <v>1437300</v>
       </c>
-      <c r="R61" s="6">
+      <c r="S61" s="6">
         <v>1859800</v>
       </c>
-      <c r="S61" s="6">
+      <c r="T61" s="6">
         <v>1959200</v>
       </c>
-      <c r="T61" s="6">
+      <c r="U61" s="6">
         <v>1593600</v>
       </c>
-      <c r="U61" s="6">
+      <c r="V61" s="6">
         <v>1299300</v>
       </c>
-      <c r="V61" s="6">
+      <c r="W61" s="6">
         <v>1298900</v>
       </c>
-      <c r="W61" s="6">
+      <c r="X61" s="6">
         <v>1298500</v>
       </c>
-      <c r="X61" s="6">
+      <c r="Y61" s="6">
         <v>1138800</v>
       </c>
-      <c r="Y61" s="6">
+      <c r="Z61" s="6">
         <v>1135200</v>
       </c>
-      <c r="Z61" s="6">
+      <c r="AA61" s="6">
         <v>869100</v>
       </c>
-      <c r="AA61" s="6">
+      <c r="AB61" s="6">
         <v>868600</v>
       </c>
-      <c r="AB61" s="6">
+      <c r="AC61" s="6">
         <v>868100</v>
       </c>
-      <c r="AC61" s="6">
+      <c r="AD61" s="6">
         <v>867600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>914600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1213400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1237900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1312400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1411300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1486700</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>66600</v>
+      </c>
+      <c r="E62" s="3">
         <v>62000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>55600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>273400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>245700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>355000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>348100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>332000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>313900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>322900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>311300</v>
       </c>
-      <c r="N62" s="6">
+      <c r="O62" s="6">
         <v>656000</v>
       </c>
-      <c r="O62" s="6">
+      <c r="P62" s="6">
         <v>625200</v>
       </c>
-      <c r="P62" s="6">
+      <c r="Q62" s="6">
         <v>623500</v>
       </c>
-      <c r="Q62" s="6">
+      <c r="R62" s="6">
         <v>619100</v>
       </c>
-      <c r="R62" s="6">
+      <c r="S62" s="6">
         <v>598600</v>
       </c>
-      <c r="S62" s="6">
+      <c r="T62" s="6">
         <v>655400</v>
       </c>
-      <c r="T62" s="6">
+      <c r="U62" s="6">
         <v>696100</v>
       </c>
-      <c r="U62" s="6">
+      <c r="V62" s="6">
         <v>741100</v>
       </c>
-      <c r="V62" s="6">
+      <c r="W62" s="6">
         <v>769100</v>
       </c>
-      <c r="W62" s="6">
+      <c r="X62" s="6">
         <v>751500</v>
       </c>
-      <c r="X62" s="6">
+      <c r="Y62" s="6">
         <v>721000</v>
       </c>
-      <c r="Y62" s="6">
+      <c r="Z62" s="6">
         <v>719100</v>
       </c>
-      <c r="Z62" s="6">
+      <c r="AA62" s="6">
         <v>734900</v>
       </c>
-      <c r="AA62" s="6">
+      <c r="AB62" s="6">
         <v>714900</v>
       </c>
-      <c r="AB62" s="6">
+      <c r="AC62" s="6">
         <v>701200</v>
       </c>
-      <c r="AC62" s="6">
+      <c r="AD62" s="6">
         <v>609100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>563400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>545900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>573800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>790400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>778700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>839500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>56200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6052,7 +6201,7 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="6">
+      <c r="N63" s="3">
         <v>0</v>
       </c>
       <c r="O63" s="6">
@@ -6100,7 +6249,7 @@
       <c r="AC63" s="6">
         <v>0</v>
       </c>
-      <c r="AD63" s="3">
+      <c r="AD63" s="6">
         <v>0</v>
       </c>
       <c r="AE63" s="3">
@@ -6124,8 +6273,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6159,7 +6311,7 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="6">
+      <c r="N64" s="3">
         <v>0</v>
       </c>
       <c r="O64" s="6">
@@ -6207,7 +6359,7 @@
       <c r="AC64" s="6">
         <v>0</v>
       </c>
-      <c r="AD64" s="3">
+      <c r="AD64" s="6">
         <v>0</v>
       </c>
       <c r="AE64" s="3">
@@ -6231,8 +6383,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6266,7 +6421,7 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="6">
+      <c r="N65" s="3">
         <v>0</v>
       </c>
       <c r="O65" s="6">
@@ -6314,7 +6469,7 @@
       <c r="AC65" s="6">
         <v>0</v>
       </c>
-      <c r="AD65" s="3">
+      <c r="AD65" s="6">
         <v>0</v>
       </c>
       <c r="AE65" s="3">
@@ -6338,115 +6493,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4983500</v>
+      </c>
+      <c r="E66" s="3">
         <v>5697100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4167000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4183700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4383200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4215200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3509500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4503200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5233900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4128000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3502500</v>
       </c>
-      <c r="N66" s="6">
+      <c r="O66" s="6">
         <v>3944200</v>
       </c>
-      <c r="O66" s="6">
+      <c r="P66" s="6">
         <v>3531500</v>
       </c>
-      <c r="P66" s="6">
+      <c r="Q66" s="6">
         <v>4364800</v>
       </c>
-      <c r="Q66" s="6">
+      <c r="R66" s="6">
         <v>3533600</v>
       </c>
-      <c r="R66" s="6">
+      <c r="S66" s="6">
         <v>4003600</v>
       </c>
-      <c r="S66" s="6">
+      <c r="T66" s="6">
         <v>4214200</v>
       </c>
-      <c r="T66" s="6">
+      <c r="U66" s="6">
         <v>4630800</v>
       </c>
-      <c r="U66" s="6">
+      <c r="V66" s="6">
         <v>3209700</v>
       </c>
-      <c r="V66" s="6">
+      <c r="W66" s="6">
         <v>4085700</v>
       </c>
-      <c r="W66" s="6">
+      <c r="X66" s="6">
         <v>3654000</v>
       </c>
-      <c r="X66" s="6">
+      <c r="Y66" s="6">
         <v>3553900</v>
       </c>
-      <c r="Y66" s="6">
+      <c r="Z66" s="6">
         <v>3167600</v>
       </c>
-      <c r="Z66" s="6">
+      <c r="AA66" s="6">
         <v>2732300</v>
       </c>
-      <c r="AA66" s="6">
+      <c r="AB66" s="6">
         <v>2080000</v>
       </c>
-      <c r="AB66" s="6">
+      <c r="AC66" s="6">
         <v>1927400</v>
       </c>
-      <c r="AC66" s="6">
+      <c r="AD66" s="6">
         <v>1758300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2167300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2153000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2155100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2350200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2578900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2599700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>158700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>151800</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6460,7 +6621,7 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-      <c r="N67" s="6"/>
+      <c r="N67" s="3"/>
       <c r="O67" s="6"/>
       <c r="P67" s="6"/>
       <c r="Q67" s="6"/>
@@ -6476,7 +6637,7 @@
       <c r="AA67" s="6"/>
       <c r="AB67" s="6"/>
       <c r="AC67" s="6"/>
-      <c r="AD67" s="3"/>
+      <c r="AD67" s="6"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
@@ -6484,8 +6645,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6519,7 +6681,7 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="6">
+      <c r="N68" s="3">
         <v>0</v>
       </c>
       <c r="O68" s="6">
@@ -6567,7 +6729,7 @@
       <c r="AC68" s="6">
         <v>0</v>
       </c>
-      <c r="AD68" s="3">
+      <c r="AD68" s="6">
         <v>0</v>
       </c>
       <c r="AE68" s="3">
@@ -6591,8 +6753,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6626,7 +6791,7 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="6">
+      <c r="N69" s="3">
         <v>0</v>
       </c>
       <c r="O69" s="6">
@@ -6674,7 +6839,7 @@
       <c r="AC69" s="6">
         <v>0</v>
       </c>
-      <c r="AD69" s="3">
+      <c r="AD69" s="6">
         <v>0</v>
       </c>
       <c r="AE69" s="3">
@@ -6698,8 +6863,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6733,7 +6901,7 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="6">
+      <c r="N70" s="3">
         <v>0</v>
       </c>
       <c r="O70" s="6">
@@ -6781,7 +6949,7 @@
       <c r="AC70" s="6">
         <v>0</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AD70" s="6">
         <v>0</v>
       </c>
       <c r="AE70" s="3">
@@ -6805,8 +6973,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6840,7 +7011,7 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="6">
+      <c r="N71" s="3">
         <v>0</v>
       </c>
       <c r="O71" s="6">
@@ -6888,7 +7059,7 @@
       <c r="AC71" s="6">
         <v>0</v>
       </c>
-      <c r="AD71" s="3">
+      <c r="AD71" s="6">
         <v>0</v>
       </c>
       <c r="AE71" s="3">
@@ -6912,115 +7083,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4131000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3853500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3543600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3394100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3168900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3000100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2815900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2910600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2758400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2676200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2525200</v>
       </c>
-      <c r="N72" s="6">
+      <c r="O72" s="6">
         <v>2555500</v>
       </c>
-      <c r="O72" s="6">
+      <c r="P72" s="6">
         <v>2405800</v>
       </c>
-      <c r="P72" s="6">
+      <c r="Q72" s="6">
         <v>2291200</v>
       </c>
-      <c r="Q72" s="6">
+      <c r="R72" s="6">
         <v>2171100</v>
       </c>
-      <c r="R72" s="6">
+      <c r="S72" s="6">
         <v>2064800</v>
       </c>
-      <c r="S72" s="6">
+      <c r="T72" s="6">
         <v>1968000</v>
       </c>
-      <c r="T72" s="6">
+      <c r="U72" s="6">
         <v>2203700</v>
       </c>
-      <c r="U72" s="6">
+      <c r="V72" s="6">
         <v>2145500</v>
       </c>
-      <c r="V72" s="6">
+      <c r="W72" s="6">
         <v>2031100</v>
       </c>
-      <c r="W72" s="6">
+      <c r="X72" s="6">
         <v>1962200</v>
       </c>
-      <c r="X72" s="6">
+      <c r="Y72" s="6">
         <v>1901700</v>
       </c>
-      <c r="Y72" s="6">
+      <c r="Z72" s="6">
         <v>1809800</v>
       </c>
-      <c r="Z72" s="6">
+      <c r="AA72" s="6">
         <v>1767800</v>
       </c>
-      <c r="AA72" s="6">
+      <c r="AB72" s="6">
         <v>1703700</v>
       </c>
-      <c r="AB72" s="6">
+      <c r="AC72" s="6">
         <v>1629600</v>
       </c>
-      <c r="AC72" s="6">
+      <c r="AD72" s="6">
         <v>1512600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1134000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1080800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>993300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>766900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>737300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>697700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>710800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>686000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7054,7 +7231,7 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="6">
+      <c r="N73" s="3">
         <v>0</v>
       </c>
       <c r="O73" s="6">
@@ -7102,7 +7279,7 @@
       <c r="AC73" s="6">
         <v>0</v>
       </c>
-      <c r="AD73" s="3">
+      <c r="AD73" s="6">
         <v>0</v>
       </c>
       <c r="AE73" s="3">
@@ -7126,8 +7303,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7161,7 +7341,7 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="6">
+      <c r="N74" s="3">
         <v>0</v>
       </c>
       <c r="O74" s="6">
@@ -7209,7 +7389,7 @@
       <c r="AC74" s="6">
         <v>0</v>
       </c>
-      <c r="AD74" s="3">
+      <c r="AD74" s="6">
         <v>0</v>
       </c>
       <c r="AE74" s="3">
@@ -7233,8 +7413,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7268,7 +7451,7 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="6">
+      <c r="N75" s="3">
         <v>0</v>
       </c>
       <c r="O75" s="6">
@@ -7316,7 +7499,7 @@
       <c r="AC75" s="6">
         <v>0</v>
       </c>
-      <c r="AD75" s="3">
+      <c r="AD75" s="6">
         <v>0</v>
       </c>
       <c r="AE75" s="3">
@@ -7340,115 +7523,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5625800</v>
+      </c>
+      <c r="E76" s="3">
         <v>5373500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5138300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4884900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4665100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4452100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4279600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4208300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4021700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4024100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3985000</v>
       </c>
-      <c r="N76" s="6">
+      <c r="O76" s="6">
         <v>3788300</v>
       </c>
-      <c r="O76" s="6">
+      <c r="P76" s="6">
         <v>3664400</v>
       </c>
-      <c r="P76" s="6">
+      <c r="Q76" s="6">
         <v>3538700</v>
       </c>
-      <c r="Q76" s="6">
+      <c r="R76" s="6">
         <v>3465300</v>
       </c>
-      <c r="R76" s="6">
+      <c r="S76" s="6">
         <v>3293800</v>
       </c>
-      <c r="S76" s="6">
+      <c r="T76" s="6">
         <v>3261900</v>
       </c>
-      <c r="T76" s="6">
+      <c r="U76" s="6">
         <v>3567300</v>
       </c>
-      <c r="U76" s="6">
+      <c r="V76" s="6">
         <v>3604800</v>
       </c>
-      <c r="V76" s="6">
+      <c r="W76" s="6">
         <v>3497000</v>
       </c>
-      <c r="W76" s="6">
+      <c r="X76" s="6">
         <v>3442500</v>
       </c>
-      <c r="X76" s="6">
+      <c r="Y76" s="6">
         <v>3404200</v>
       </c>
-      <c r="Y76" s="6">
+      <c r="Z76" s="6">
         <v>3348900</v>
       </c>
-      <c r="Z76" s="6">
+      <c r="AA76" s="6">
         <v>3344500</v>
       </c>
-      <c r="AA76" s="6">
+      <c r="AB76" s="6">
         <v>3286300</v>
       </c>
-      <c r="AB76" s="6">
+      <c r="AC76" s="6">
         <v>3310100</v>
       </c>
-      <c r="AC76" s="6">
+      <c r="AD76" s="6">
         <v>3355600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3149600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3175200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3110600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2877900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2816700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2745400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>317900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>289600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7482,7 +7671,7 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="6">
+      <c r="N77" s="3">
         <v>0</v>
       </c>
       <c r="O77" s="6">
@@ -7530,7 +7719,7 @@
       <c r="AC77" s="6">
         <v>0</v>
       </c>
-      <c r="AD77" s="3">
+      <c r="AD77" s="6">
         <v>0</v>
       </c>
       <c r="AE77" s="3">
@@ -7554,227 +7743,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.25">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="5">
+      <c r="O80" s="5">
         <v>45199</v>
       </c>
-      <c r="O80" s="5">
+      <c r="P80" s="5">
         <v>45107</v>
       </c>
-      <c r="P80" s="5">
+      <c r="Q80" s="5">
         <v>45016</v>
       </c>
-      <c r="Q80" s="5">
+      <c r="R80" s="5">
         <v>44926</v>
       </c>
-      <c r="R80" s="5">
+      <c r="S80" s="5">
         <v>44834</v>
       </c>
-      <c r="S80" s="5">
+      <c r="T80" s="5">
         <v>44742</v>
       </c>
-      <c r="T80" s="5">
+      <c r="U80" s="5">
         <v>44651</v>
       </c>
-      <c r="U80" s="5">
+      <c r="V80" s="5">
         <v>44561</v>
       </c>
-      <c r="V80" s="5">
+      <c r="W80" s="5">
         <v>44469</v>
       </c>
-      <c r="W80" s="5">
+      <c r="X80" s="5">
         <v>44377</v>
       </c>
-      <c r="X80" s="5">
+      <c r="Y80" s="5">
         <v>44286</v>
       </c>
-      <c r="Y80" s="5">
+      <c r="Z80" s="5">
         <v>44196</v>
       </c>
-      <c r="Z80" s="5">
+      <c r="AA80" s="5">
         <v>44104</v>
       </c>
-      <c r="AA80" s="5">
+      <c r="AB80" s="5">
         <v>44012</v>
       </c>
-      <c r="AB80" s="5">
+      <c r="AC80" s="5">
         <v>43921</v>
       </c>
-      <c r="AC80" s="5">
+      <c r="AD80" s="5">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>353100</v>
+      </c>
+      <c r="E81" s="3">
         <v>385700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>313500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>300800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>235100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>250600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>196500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>218500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>140400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>209500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>212000</v>
       </c>
-      <c r="N81" s="6">
+      <c r="O81" s="6">
         <v>207100</v>
       </c>
-      <c r="O81" s="6">
+      <c r="P81" s="6">
         <v>167000</v>
       </c>
-      <c r="P81" s="6">
+      <c r="Q81" s="6">
         <v>172600</v>
       </c>
-      <c r="Q81" s="6">
+      <c r="R81" s="6">
         <v>159400</v>
       </c>
-      <c r="R81" s="6">
+      <c r="S81" s="6">
         <v>149600</v>
       </c>
-      <c r="S81" s="6">
+      <c r="T81" s="6">
         <v>-184500</v>
       </c>
-      <c r="T81" s="6">
+      <c r="U81" s="6">
         <v>109200</v>
       </c>
-      <c r="U81" s="6">
+      <c r="V81" s="6">
         <v>165300</v>
       </c>
-      <c r="V81" s="6">
+      <c r="W81" s="6">
         <v>120000</v>
       </c>
-      <c r="W81" s="6">
+      <c r="X81" s="6">
         <v>105200</v>
       </c>
-      <c r="X81" s="6">
+      <c r="Y81" s="6">
         <v>136800</v>
       </c>
-      <c r="Y81" s="6">
+      <c r="Z81" s="6">
         <v>87100</v>
       </c>
-      <c r="Z81" s="6">
+      <c r="AA81" s="6">
         <v>109600</v>
       </c>
-      <c r="AA81" s="6">
+      <c r="AB81" s="6">
         <v>113300</v>
       </c>
-      <c r="AB81" s="6">
+      <c r="AC81" s="6">
         <v>157000</v>
       </c>
-      <c r="AC81" s="6">
+      <c r="AD81" s="6">
         <v>86100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>82400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>117300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>254600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>59700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>67300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>45000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>40300</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7788,7 +7986,7 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-      <c r="N82" s="6"/>
+      <c r="N82" s="3"/>
       <c r="O82" s="6"/>
       <c r="P82" s="6"/>
       <c r="Q82" s="6"/>
@@ -7804,7 +8002,7 @@
       <c r="AA82" s="6"/>
       <c r="AB82" s="6"/>
       <c r="AC82" s="6"/>
-      <c r="AD82" s="3"/>
+      <c r="AD82" s="6"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
@@ -7812,115 +8010,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E83" s="3">
         <v>9400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9500</v>
       </c>
-      <c r="N83" s="6">
+      <c r="O83" s="6">
         <v>38800</v>
       </c>
-      <c r="O83" s="6">
+      <c r="P83" s="6">
         <v>39800</v>
       </c>
-      <c r="P83" s="6">
+      <c r="Q83" s="6">
         <v>41400</v>
       </c>
-      <c r="Q83" s="6">
+      <c r="R83" s="6">
         <v>44700</v>
       </c>
-      <c r="R83" s="6">
+      <c r="S83" s="6">
         <v>41000</v>
       </c>
-      <c r="S83" s="6">
+      <c r="T83" s="6">
         <v>40200</v>
       </c>
-      <c r="T83" s="6">
+      <c r="U83" s="6">
         <v>40900</v>
       </c>
-      <c r="U83" s="6">
+      <c r="V83" s="6">
         <v>42000</v>
       </c>
-      <c r="V83" s="6">
+      <c r="W83" s="6">
         <v>42800</v>
       </c>
-      <c r="W83" s="6">
+      <c r="X83" s="6">
         <v>40600</v>
       </c>
-      <c r="X83" s="6">
+      <c r="Y83" s="6">
         <v>42000</v>
       </c>
-      <c r="Y83" s="6">
+      <c r="Z83" s="6">
         <v>40500</v>
       </c>
-      <c r="Z83" s="6">
+      <c r="AA83" s="6">
         <v>39500</v>
       </c>
-      <c r="AA83" s="6">
+      <c r="AB83" s="6">
         <v>38000</v>
       </c>
-      <c r="AB83" s="6">
+      <c r="AC83" s="6">
         <v>40500</v>
       </c>
-      <c r="AC83" s="6">
+      <c r="AD83" s="6">
         <v>42800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>50400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>54200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>55900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>55400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>55800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>25100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>10100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7954,7 +8156,7 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="6">
+      <c r="N84" s="3">
         <v>0</v>
       </c>
       <c r="O84" s="6">
@@ -8002,7 +8204,7 @@
       <c r="AC84" s="6">
         <v>0</v>
       </c>
-      <c r="AD84" s="3">
+      <c r="AD84" s="6">
         <v>0</v>
       </c>
       <c r="AE84" s="3">
@@ -8026,8 +8228,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8061,7 +8266,7 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="6">
+      <c r="N85" s="3">
         <v>0</v>
       </c>
       <c r="O85" s="6">
@@ -8109,7 +8314,7 @@
       <c r="AC85" s="6">
         <v>0</v>
       </c>
-      <c r="AD85" s="3">
+      <c r="AD85" s="6">
         <v>0</v>
       </c>
       <c r="AE85" s="3">
@@ -8133,8 +8338,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8168,7 +8376,7 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="6">
+      <c r="N86" s="3">
         <v>0</v>
       </c>
       <c r="O86" s="6">
@@ -8216,7 +8424,7 @@
       <c r="AC86" s="6">
         <v>0</v>
       </c>
-      <c r="AD86" s="3">
+      <c r="AD86" s="6">
         <v>0</v>
       </c>
       <c r="AE86" s="3">
@@ -8240,8 +8448,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8275,7 +8486,7 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="6">
+      <c r="N87" s="3">
         <v>0</v>
       </c>
       <c r="O87" s="6">
@@ -8323,7 +8534,7 @@
       <c r="AC87" s="6">
         <v>0</v>
       </c>
-      <c r="AD87" s="3">
+      <c r="AD87" s="6">
         <v>0</v>
       </c>
       <c r="AE87" s="3">
@@ -8347,8 +8558,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8382,7 +8596,7 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="6">
+      <c r="N88" s="3">
         <v>0</v>
       </c>
       <c r="O88" s="6">
@@ -8430,7 +8644,7 @@
       <c r="AC88" s="6">
         <v>0</v>
       </c>
-      <c r="AD88" s="3">
+      <c r="AD88" s="6">
         <v>0</v>
       </c>
       <c r="AE88" s="3">
@@ -8454,115 +8668,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-503200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1960000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>352100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>153900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>333700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>912900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-710400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-578500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1493900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>895600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-189000</v>
       </c>
-      <c r="N89" s="6">
+      <c r="O89" s="6">
         <v>736900</v>
       </c>
-      <c r="O89" s="6">
+      <c r="P89" s="6">
         <v>-503100</v>
       </c>
-      <c r="P89" s="6">
+      <c r="Q89" s="6">
         <v>1030800</v>
       </c>
-      <c r="Q89" s="6">
+      <c r="R89" s="6">
         <v>-143600</v>
       </c>
-      <c r="R89" s="6">
+      <c r="S89" s="6">
         <v>169300</v>
       </c>
-      <c r="S89" s="6">
+      <c r="T89" s="6">
         <v>-634400</v>
       </c>
-      <c r="T89" s="6">
+      <c r="U89" s="6">
         <v>1259800</v>
       </c>
-      <c r="U89" s="6">
+      <c r="V89" s="6">
         <v>-688600</v>
       </c>
-      <c r="V89" s="6">
+      <c r="W89" s="6">
         <v>563600</v>
       </c>
-      <c r="W89" s="6">
+      <c r="X89" s="6">
         <v>122700</v>
       </c>
-      <c r="X89" s="6">
+      <c r="Y89" s="6">
         <v>599100</v>
       </c>
-      <c r="Y89" s="6">
+      <c r="Z89" s="6">
         <v>269400</v>
       </c>
-      <c r="Z89" s="6">
+      <c r="AA89" s="6">
         <v>701100</v>
       </c>
-      <c r="AA89" s="6">
+      <c r="AB89" s="6">
         <v>325000</v>
       </c>
-      <c r="AB89" s="6">
+      <c r="AC89" s="6">
         <v>163300</v>
       </c>
-      <c r="AC89" s="6">
+      <c r="AD89" s="6">
         <v>237700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>185800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>163500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>195500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>189800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-17700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>55400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8576,7 +8796,7 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-      <c r="N90" s="6"/>
+      <c r="N90" s="3"/>
       <c r="O90" s="6"/>
       <c r="P90" s="6"/>
       <c r="Q90" s="6"/>
@@ -8592,7 +8812,7 @@
       <c r="AA90" s="6"/>
       <c r="AB90" s="6"/>
       <c r="AC90" s="6"/>
-      <c r="AD90" s="3"/>
+      <c r="AD90" s="6"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
@@ -8600,115 +8820,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17100</v>
       </c>
-      <c r="N91" s="6">
+      <c r="O91" s="6">
         <v>-7700</v>
       </c>
-      <c r="O91" s="6">
+      <c r="P91" s="6">
         <v>-7800</v>
       </c>
-      <c r="P91" s="6">
+      <c r="Q91" s="6">
         <v>-12400</v>
       </c>
-      <c r="Q91" s="6">
+      <c r="R91" s="6">
         <v>-27400</v>
       </c>
-      <c r="R91" s="6">
+      <c r="S91" s="6">
         <v>-10200</v>
       </c>
-      <c r="S91" s="6">
+      <c r="T91" s="6">
         <v>-11400</v>
       </c>
-      <c r="T91" s="6">
+      <c r="U91" s="6">
         <v>-10800</v>
       </c>
-      <c r="U91" s="6">
+      <c r="V91" s="6">
         <v>-13700</v>
       </c>
-      <c r="V91" s="6">
+      <c r="W91" s="6">
         <v>-16000</v>
       </c>
-      <c r="W91" s="6">
+      <c r="X91" s="6">
         <v>-11400</v>
       </c>
-      <c r="X91" s="6">
+      <c r="Y91" s="6">
         <v>-9900</v>
       </c>
-      <c r="Y91" s="6">
+      <c r="Z91" s="6">
         <v>-10200</v>
       </c>
-      <c r="Z91" s="6">
+      <c r="AA91" s="6">
         <v>-20000</v>
       </c>
-      <c r="AA91" s="6">
+      <c r="AB91" s="6">
         <v>-6600</v>
       </c>
-      <c r="AB91" s="6">
+      <c r="AC91" s="6">
         <v>-10600</v>
       </c>
-      <c r="AC91" s="6">
+      <c r="AD91" s="6">
         <v>-8200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8742,7 +8966,7 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="6">
+      <c r="N92" s="3">
         <v>0</v>
       </c>
       <c r="O92" s="6">
@@ -8790,7 +9014,7 @@
       <c r="AC92" s="6">
         <v>0</v>
       </c>
-      <c r="AD92" s="3">
+      <c r="AD92" s="6">
         <v>0</v>
       </c>
       <c r="AE92" s="3">
@@ -8814,8 +9038,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8849,7 +9076,7 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="6">
+      <c r="N93" s="3">
         <v>0</v>
       </c>
       <c r="O93" s="6">
@@ -8897,7 +9124,7 @@
       <c r="AC93" s="6">
         <v>0</v>
       </c>
-      <c r="AD93" s="3">
+      <c r="AD93" s="6">
         <v>0</v>
       </c>
       <c r="AE93" s="3">
@@ -8921,115 +9148,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-106900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>419300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>167500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-116900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-126800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>35400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-37100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-38200</v>
       </c>
-      <c r="N94" s="6">
+      <c r="O94" s="6">
         <v>25900</v>
       </c>
-      <c r="O94" s="6">
+      <c r="P94" s="6">
         <v>-44700</v>
       </c>
-      <c r="P94" s="6">
+      <c r="Q94" s="6">
         <v>1900</v>
       </c>
-      <c r="Q94" s="6">
+      <c r="R94" s="6">
         <v>-90500</v>
       </c>
-      <c r="R94" s="6">
+      <c r="S94" s="6">
         <v>28300</v>
       </c>
-      <c r="S94" s="6">
+      <c r="T94" s="6">
         <v>-748000</v>
       </c>
-      <c r="T94" s="6">
+      <c r="U94" s="6">
         <v>-24900</v>
       </c>
-      <c r="U94" s="6">
+      <c r="V94" s="6">
         <v>-216200</v>
       </c>
-      <c r="V94" s="6">
+      <c r="W94" s="6">
         <v>-90700</v>
       </c>
-      <c r="W94" s="6">
+      <c r="X94" s="6">
         <v>-32500</v>
       </c>
-      <c r="X94" s="6">
+      <c r="Y94" s="6">
         <v>-13300</v>
       </c>
-      <c r="Y94" s="6">
+      <c r="Z94" s="6">
         <v>-325900</v>
       </c>
-      <c r="Z94" s="6">
+      <c r="AA94" s="6">
         <v>87000</v>
       </c>
-      <c r="AA94" s="6">
+      <c r="AB94" s="6">
         <v>-140600</v>
       </c>
-      <c r="AB94" s="6">
+      <c r="AC94" s="6">
         <v>-51000</v>
       </c>
-      <c r="AC94" s="6">
+      <c r="AD94" s="6">
         <v>-47200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-72200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-25200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-66900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>97800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-80600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1386800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9043,7 +9276,7 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-      <c r="N95" s="6"/>
+      <c r="N95" s="3"/>
       <c r="O95" s="6"/>
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
@@ -9059,7 +9292,7 @@
       <c r="AA95" s="6"/>
       <c r="AB95" s="6"/>
       <c r="AC95" s="6"/>
-      <c r="AD95" s="3"/>
+      <c r="AD95" s="6"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
@@ -9067,22 +9300,23 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>75800</v>
+        <v>75700</v>
       </c>
       <c r="E96" s="3">
         <v>75800</v>
       </c>
       <c r="F96" s="3">
+        <v>75800</v>
+      </c>
+      <c r="G96" s="3">
         <v>75700</v>
-      </c>
-      <c r="G96" s="3">
-        <v>66400</v>
       </c>
       <c r="H96" s="3">
         <v>66400</v>
@@ -9091,91 +9325,94 @@
         <v>66400</v>
       </c>
       <c r="J96" s="3">
+        <v>66400</v>
+      </c>
+      <c r="K96" s="3">
         <v>66300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>58200</v>
-      </c>
-      <c r="L96" s="3">
-        <v>58500</v>
       </c>
       <c r="M96" s="3">
         <v>58500</v>
       </c>
-      <c r="N96" s="6">
+      <c r="N96" s="3">
+        <v>58500</v>
+      </c>
+      <c r="O96" s="6">
         <v>-58500</v>
       </c>
-      <c r="O96" s="6">
+      <c r="P96" s="6">
         <v>-53200</v>
       </c>
-      <c r="P96" s="6">
+      <c r="Q96" s="6">
         <v>-53300</v>
-      </c>
-      <c r="Q96" s="6">
-        <v>-53400</v>
       </c>
       <c r="R96" s="6">
         <v>-53400</v>
       </c>
       <c r="S96" s="6">
+        <v>-53400</v>
+      </c>
+      <c r="T96" s="6">
         <v>-51200</v>
       </c>
-      <c r="T96" s="6">
+      <c r="U96" s="6">
         <v>-51400</v>
-      </c>
-      <c r="U96" s="6">
-        <v>-51500</v>
       </c>
       <c r="V96" s="6">
         <v>-51500</v>
       </c>
       <c r="W96" s="6">
+        <v>-51500</v>
+      </c>
+      <c r="X96" s="6">
         <v>-45000</v>
-      </c>
-      <c r="X96" s="6">
-        <v>-45300</v>
       </c>
       <c r="Y96" s="6">
         <v>-45300</v>
       </c>
       <c r="Z96" s="6">
+        <v>-45300</v>
+      </c>
+      <c r="AA96" s="6">
         <v>-45800</v>
       </c>
-      <c r="AA96" s="6">
+      <c r="AB96" s="6">
         <v>-39500</v>
-      </c>
-      <c r="AB96" s="6">
-        <v>-40000</v>
       </c>
       <c r="AC96" s="6">
         <v>-40000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AD96" s="6">
+        <v>-40000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-30400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-30600</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-30700</v>
       </c>
       <c r="AG96" s="3">
         <v>-30700</v>
       </c>
       <c r="AH96" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-28400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-28300</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-20400</v>
       </c>
       <c r="AK96" s="3">
         <v>-20400</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-20400</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9209,7 +9446,7 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N97" s="3">
         <v>0</v>
       </c>
       <c r="O97" s="6">
@@ -9257,7 +9494,7 @@
       <c r="AC97" s="6">
         <v>0</v>
       </c>
-      <c r="AD97" s="3">
+      <c r="AD97" s="6">
         <v>0</v>
       </c>
       <c r="AE97" s="3">
@@ -9281,8 +9518,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9316,7 +9556,7 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="6">
+      <c r="N98" s="3">
         <v>0</v>
       </c>
       <c r="O98" s="6">
@@ -9364,7 +9604,7 @@
       <c r="AC98" s="6">
         <v>0</v>
       </c>
-      <c r="AD98" s="3">
+      <c r="AD98" s="6">
         <v>0</v>
       </c>
       <c r="AE98" s="3">
@@ -9388,8 +9628,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9423,7 +9666,7 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="6">
+      <c r="N99" s="3">
         <v>0</v>
       </c>
       <c r="O99" s="6">
@@ -9471,7 +9714,7 @@
       <c r="AC99" s="6">
         <v>0</v>
       </c>
-      <c r="AD99" s="3">
+      <c r="AD99" s="6">
         <v>0</v>
       </c>
       <c r="AE99" s="3">
@@ -9495,325 +9738,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-111600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-140200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-77500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-75800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-103800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-114500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-70700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-78100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-177600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-168600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-142500</v>
       </c>
-      <c r="N100" s="6">
+      <c r="O100" s="6">
         <v>-164900</v>
       </c>
-      <c r="O100" s="6">
+      <c r="P100" s="6">
         <v>-207500</v>
       </c>
-      <c r="P100" s="6">
+      <c r="Q100" s="6">
         <v>-141200</v>
       </c>
-      <c r="Q100" s="6">
+      <c r="R100" s="6">
         <v>-193000</v>
       </c>
-      <c r="R100" s="6">
+      <c r="S100" s="6">
         <v>-161100</v>
       </c>
-      <c r="S100" s="6">
+      <c r="T100" s="6">
         <v>289300</v>
       </c>
-      <c r="T100" s="6">
+      <c r="U100" s="6">
         <v>146500</v>
       </c>
-      <c r="U100" s="6">
+      <c r="V100" s="6">
         <v>-53800</v>
       </c>
-      <c r="V100" s="6">
+      <c r="W100" s="6">
         <v>-52400</v>
       </c>
-      <c r="W100" s="6">
+      <c r="X100" s="6">
         <v>25400</v>
       </c>
-      <c r="X100" s="6">
+      <c r="Y100" s="6">
         <v>-119500</v>
       </c>
-      <c r="Y100" s="6">
+      <c r="Z100" s="6">
         <v>130900</v>
       </c>
-      <c r="Z100" s="6">
+      <c r="AA100" s="6">
         <v>-17700</v>
       </c>
-      <c r="AA100" s="6">
+      <c r="AB100" s="6">
         <v>-139200</v>
       </c>
-      <c r="AB100" s="6">
+      <c r="AC100" s="6">
         <v>-175700</v>
       </c>
-      <c r="AC100" s="6">
+      <c r="AD100" s="6">
         <v>-113900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-135600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-114200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-114600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-132200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-111200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1457700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-23900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-25100</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>173700</v>
+      </c>
+      <c r="E101" s="3">
         <v>125700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-128500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>74800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-16400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-25000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>35100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>21100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>20500</v>
       </c>
-      <c r="N101" s="6">
+      <c r="O101" s="6">
         <v>-2600</v>
       </c>
-      <c r="O101" s="6">
+      <c r="P101" s="6">
         <v>-800</v>
       </c>
-      <c r="P101" s="6">
+      <c r="Q101" s="6">
         <v>21100</v>
       </c>
-      <c r="Q101" s="6">
+      <c r="R101" s="6">
         <v>20500</v>
       </c>
-      <c r="R101" s="6">
+      <c r="S101" s="6">
         <v>-14700</v>
       </c>
-      <c r="S101" s="6">
+      <c r="T101" s="6">
         <v>-16500</v>
       </c>
-      <c r="T101" s="6">
+      <c r="U101" s="6">
         <v>700</v>
       </c>
-      <c r="U101" s="6">
+      <c r="V101" s="6">
         <v>-11600</v>
       </c>
-      <c r="V101" s="6">
+      <c r="W101" s="6">
         <v>2800</v>
       </c>
-      <c r="W101" s="6">
+      <c r="X101" s="6">
         <v>200</v>
       </c>
-      <c r="X101" s="6">
+      <c r="Y101" s="6">
         <v>-500</v>
       </c>
-      <c r="Y101" s="6">
+      <c r="Z101" s="6">
         <v>-1500</v>
       </c>
-      <c r="Z101" s="6">
+      <c r="AA101" s="6">
         <v>4100</v>
       </c>
-      <c r="AA101" s="6">
+      <c r="AB101" s="6">
         <v>-300</v>
       </c>
-      <c r="AB101" s="6">
+      <c r="AC101" s="6">
         <v>-700</v>
       </c>
-      <c r="AC101" s="6">
+      <c r="AD101" s="6">
         <v>2700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>3800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2800</v>
-      </c>
-      <c r="AJ101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK101" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL101" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-689500</v>
+      </c>
+      <c r="E102" s="3">
         <v>1744000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>698800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>213100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>286700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>904400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1036400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-546400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1262800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>688700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-334600</v>
       </c>
-      <c r="N102" s="6">
+      <c r="O102" s="6">
         <v>595300</v>
       </c>
-      <c r="O102" s="6">
+      <c r="P102" s="6">
         <v>-756100</v>
       </c>
-      <c r="P102" s="6">
+      <c r="Q102" s="6">
         <v>912600</v>
       </c>
-      <c r="Q102" s="6">
+      <c r="R102" s="6">
         <v>-406600</v>
       </c>
-      <c r="R102" s="6">
+      <c r="S102" s="6">
         <v>21800</v>
       </c>
-      <c r="S102" s="6">
+      <c r="T102" s="6">
         <v>-1109600</v>
       </c>
-      <c r="T102" s="6">
+      <c r="U102" s="6">
         <v>1382100</v>
       </c>
-      <c r="U102" s="6">
+      <c r="V102" s="6">
         <v>-970200</v>
       </c>
-      <c r="V102" s="6">
+      <c r="W102" s="6">
         <v>423300</v>
       </c>
-      <c r="W102" s="6">
+      <c r="X102" s="6">
         <v>115800</v>
       </c>
-      <c r="X102" s="6">
+      <c r="Y102" s="6">
         <v>465800</v>
       </c>
-      <c r="Y102" s="6">
+      <c r="Z102" s="6">
         <v>72900</v>
       </c>
-      <c r="Z102" s="6">
+      <c r="AA102" s="6">
         <v>774500</v>
       </c>
-      <c r="AA102" s="6">
+      <c r="AB102" s="6">
         <v>44900</v>
       </c>
-      <c r="AB102" s="6">
+      <c r="AC102" s="6">
         <v>-64100</v>
       </c>
-      <c r="AC102" s="6">
+      <c r="AD102" s="6">
         <v>79300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>22800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>18700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-23800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>56000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>24500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>20600</v>
       </c>
     </row>
